--- a/subsystems database.xlsx
+++ b/subsystems database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421765E8-A994-4544-8FA4-8B23D6129513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1497E37-3703-4A5F-A136-DE36226DD7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-795" windowWidth="29040" windowHeight="15720" xr2:uid="{DA27C19A-18DB-4E19-9AD3-8F88A97C8EE8}"/>
+    <workbookView xWindow="900" yWindow="912" windowWidth="21600" windowHeight="11232" xr2:uid="{DA27C19A-18DB-4E19-9AD3-8F88A97C8EE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
   <si>
     <t>md</t>
   </si>
@@ -105,6 +105,24 @@
   </si>
   <si>
     <t>9205-FLO-1-CLS</t>
+  </si>
+  <si>
+    <t>0609-LLPS-GRC</t>
+  </si>
+  <si>
+    <t>ND</t>
+  </si>
+  <si>
+    <t>0610-LAT-1</t>
+  </si>
+  <si>
+    <t>kW</t>
+  </si>
+  <si>
+    <t>kWh</t>
+  </si>
+  <si>
+    <t>mt</t>
   </si>
 </sst>
 </file>
@@ -186,23 +204,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -538,453 +555,646 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66EAA883-65ED-4288-9D11-90A18C3BBAF4}">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="7.28515625" customWidth="1"/>
+    <col min="4" max="11" width="11.5703125" customWidth="1"/>
+    <col min="12" max="12" width="17.85546875" customWidth="1"/>
+    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="1">
+        <f>SUM(C2:E2)</f>
+        <v>16448</v>
+      </c>
+      <c r="C2" s="1">
         <v>2373</v>
       </c>
-      <c r="C2" s="1">
+      <c r="D2" s="1">
         <v>5295</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
         <v>8780</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>2265</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>311</v>
       </c>
-      <c r="G2" s="2">
+      <c r="H2" s="4">
         <v>460</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
         <v>495</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2" s="1">
         <v>366</v>
       </c>
-      <c r="J2" s="1">
+      <c r="K2" s="1">
         <v>29</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>404</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="1">
         <v>273</v>
       </c>
-      <c r="M2" s="1"/>
+      <c r="N2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0.112</v>
+      </c>
+      <c r="P2">
+        <f>O2*75</f>
+        <v>8.4</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="1">
+        <f t="shared" ref="B3:B13" si="0">SUM(C3:E3)</f>
+        <v>5038.6000000000004</v>
+      </c>
+      <c r="C3" s="1">
         <v>1673.7</v>
       </c>
-      <c r="C3" s="1">
+      <c r="D3" s="1">
         <v>473.3</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E3" s="1">
         <v>2891.6000000000004</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F3" s="1">
         <v>1822</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G3" s="1">
         <v>333</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="4">
         <v>532.9</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <v>252.5</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>125.7</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K3" s="1">
         <v>120.1</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>113.5</v>
       </c>
-      <c r="L3" s="1">
+      <c r="M3" s="1">
         <v>56</v>
       </c>
-      <c r="M3" s="1"/>
+      <c r="N3" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="1">
+        <f t="shared" si="0"/>
+        <v>60075</v>
+      </c>
+      <c r="C4" s="1">
         <v>9823</v>
       </c>
-      <c r="C4" s="1">
+      <c r="D4" s="1">
         <v>25000</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="1">
         <v>25252</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>2100</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G4" s="1">
         <v>450</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="4">
         <v>1681</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>4258</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
         <v>478</v>
       </c>
-      <c r="J4" s="1">
+      <c r="K4" s="1">
         <v>934</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>2017</v>
       </c>
-      <c r="L4" s="1">
+      <c r="M4" s="1">
         <v>455</v>
       </c>
-      <c r="M4" s="1"/>
+      <c r="N4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" s="1">
+        <v>2</v>
+      </c>
+      <c r="P4">
+        <f>O4*3*24</f>
+        <v>144</v>
+      </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1">
+        <f t="shared" si="0"/>
+        <v>69298</v>
+      </c>
+      <c r="C5" s="1">
         <v>7899</v>
       </c>
-      <c r="C5" s="1">
+      <c r="D5" s="1">
         <v>25000</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="1">
         <v>36399</v>
       </c>
-      <c r="E5" s="1">
+      <c r="F5" s="1">
         <v>2100</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
         <v>333</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="4">
         <v>1955</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>2943</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <v>478</v>
       </c>
-      <c r="J5" s="1">
+      <c r="K5" s="1">
         <v>1062</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>1006</v>
       </c>
-      <c r="L5" s="1">
+      <c r="M5" s="1">
         <v>455</v>
       </c>
-      <c r="M5" s="1"/>
+      <c r="N5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" s="1">
+        <v>2</v>
+      </c>
+      <c r="P5">
+        <f>O5*3*24</f>
+        <v>144</v>
+      </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="1">
+        <f>SUM(C6:E6)</f>
+        <v>89365</v>
+      </c>
+      <c r="C6" s="1">
         <v>9320</v>
       </c>
-      <c r="C6" s="1">
+      <c r="D6" s="1">
         <v>35894</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="1">
         <v>44151</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
         <v>3100</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>450</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6" s="4">
         <v>1770</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>4969</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>385</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>307</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>420</v>
       </c>
-      <c r="L6" s="1">
+      <c r="M6" s="1">
         <v>1469</v>
       </c>
-      <c r="M6" s="1">
+      <c r="N6" s="1">
         <v>1878</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="1">
+        <f t="shared" si="0"/>
+        <v>44821</v>
+      </c>
+      <c r="C7" s="1">
         <v>5858</v>
       </c>
-      <c r="C7" s="1">
+      <c r="D7" s="1">
         <v>16461</v>
       </c>
-      <c r="D7" s="1">
+      <c r="E7" s="1">
         <v>22502</v>
       </c>
-      <c r="E7" s="1">
+      <c r="F7" s="1">
         <v>2260</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>379</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="4">
         <v>2822</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>1749</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>204</v>
       </c>
-      <c r="J7" s="1">
+      <c r="K7" s="1">
         <v>818</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>265</v>
       </c>
-      <c r="L7" s="1">
-        <v>0</v>
-      </c>
-      <c r="M7" s="1"/>
+      <c r="M7" s="1">
+        <v>1</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="1">
+        <f t="shared" si="0"/>
+        <v>61503</v>
+      </c>
+      <c r="C8" s="1">
         <v>7542</v>
       </c>
-      <c r="C8" s="1">
+      <c r="D8" s="1">
         <v>28475</v>
       </c>
-      <c r="D8" s="1">
+      <c r="E8" s="1">
         <v>25486</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F8" s="1">
         <v>1900</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>362</v>
       </c>
-      <c r="G8" s="2">
+      <c r="H8" s="4">
         <v>2015</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>2425</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>553</v>
       </c>
-      <c r="J8" s="1">
+      <c r="K8" s="1">
         <v>594</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>1072</v>
       </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
         <v>883</v>
       </c>
-      <c r="M8" s="1">
+      <c r="N8" s="1">
         <v>1508</v>
       </c>
+      <c r="O8" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="1">
+        <f t="shared" si="0"/>
+        <v>57620</v>
+      </c>
+      <c r="C9" s="1">
         <v>7412</v>
       </c>
-      <c r="C9" s="1">
+      <c r="D9" s="1">
         <v>26375</v>
       </c>
-      <c r="D9" s="1">
+      <c r="E9" s="1">
         <v>23833</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F9" s="1">
         <v>1900</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
         <v>351</v>
       </c>
-      <c r="G9" s="2">
+      <c r="H9" s="4">
         <v>1985</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>2347</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>553</v>
       </c>
-      <c r="J9" s="1">
+      <c r="K9" s="1">
         <v>594</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>1066</v>
       </c>
-      <c r="L9" s="1">
+      <c r="M9" s="1">
         <v>867</v>
       </c>
-      <c r="M9" s="1">
+      <c r="N9" s="1">
         <v>1483</v>
       </c>
+      <c r="O9" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="1">
+        <f t="shared" si="0"/>
+        <v>47150</v>
+      </c>
+      <c r="C10" s="1">
         <v>5970</v>
       </c>
-      <c r="C10" s="1">
+      <c r="D10" s="1">
         <v>22028</v>
       </c>
-      <c r="D10" s="1">
+      <c r="E10" s="1">
         <v>19152</v>
       </c>
-      <c r="E10" s="1">
+      <c r="F10" s="1">
         <v>1900</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="1">
         <v>363</v>
       </c>
-      <c r="G10" s="2">
+      <c r="H10" s="4">
         <v>1877</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <v>1125</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>553</v>
       </c>
-      <c r="J10" s="1">
+      <c r="K10" s="1">
         <v>594</v>
       </c>
-      <c r="K10" s="1">
+      <c r="L10" s="1">
         <v>1049</v>
       </c>
-      <c r="L10" s="1">
+      <c r="M10" s="1">
         <v>772</v>
       </c>
-      <c r="M10" s="1">
+      <c r="N10" s="1">
         <v>1194</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="1">
+        <f t="shared" si="0"/>
+        <v>45180</v>
+      </c>
+      <c r="C11" s="1">
         <v>5912</v>
       </c>
-      <c r="C11" s="1">
+      <c r="D11" s="1">
         <v>20956</v>
       </c>
-      <c r="D11" s="1">
+      <c r="E11" s="1">
         <v>18312</v>
       </c>
-      <c r="E11" s="1">
+      <c r="F11" s="1">
         <v>1900</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G11" s="1">
         <v>363</v>
       </c>
-      <c r="G11" s="2">
+      <c r="H11" s="4">
         <v>1860</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>1095</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11" s="1">
         <v>553</v>
       </c>
-      <c r="J11" s="1">
+      <c r="K11" s="1">
         <v>594</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>1046</v>
       </c>
-      <c r="L11" s="1">
+      <c r="M11" s="1">
         <v>764</v>
       </c>
-      <c r="M11" s="1">
+      <c r="N11" s="1">
         <v>1182</v>
+      </c>
+      <c r="O11" s="1">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="1">
+        <f t="shared" si="0"/>
+        <v>11180</v>
+      </c>
+      <c r="C12" s="1">
+        <v>6503</v>
+      </c>
+      <c r="D12" s="1">
+        <v>229</v>
+      </c>
+      <c r="E12" s="1">
+        <v>4448</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="1">
+        <v>450</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1186.3399999999999</v>
+      </c>
+      <c r="I12" s="1">
+        <v>918.21</v>
+      </c>
+      <c r="J12" s="1">
+        <v>663</v>
+      </c>
+      <c r="K12" s="1">
+        <v>258.7</v>
+      </c>
+      <c r="L12" s="1">
+        <v>459.04</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1">
+        <v>472</v>
+      </c>
+      <c r="O12" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="1">
+        <f t="shared" si="0"/>
+        <v>83417</v>
+      </c>
+      <c r="C13" s="1">
+        <v>10747</v>
+      </c>
+      <c r="D13" s="1">
+        <v>22074</v>
+      </c>
+      <c r="E13" s="1">
+        <v>50596</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="1">
+        <v>450</v>
+      </c>
+      <c r="H13" s="1">
+        <v>453</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2969</v>
+      </c>
+      <c r="J13" s="1">
+        <v>288</v>
+      </c>
+      <c r="K13" s="1">
+        <v>519</v>
+      </c>
+      <c r="L13" s="1">
+        <v>56</v>
+      </c>
+      <c r="M13" s="1">
+        <v>527</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O13" s="1">
+        <v>3</v>
+      </c>
+      <c r="P13">
+        <f>O13*8.3</f>
+        <v>24.900000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/subsystems database.xlsx
+++ b/subsystems database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1497E37-3703-4A5F-A136-DE36226DD7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63B9E34-114B-4DFB-8C8F-8C4BB93820D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="912" windowWidth="21600" windowHeight="11232" xr2:uid="{DA27C19A-18DB-4E19-9AD3-8F88A97C8EE8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DA27C19A-18DB-4E19-9AD3-8F88A97C8EE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t>md</t>
   </si>
@@ -138,12 +138,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -204,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -219,6 +225,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -556,18 +565,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66EAA883-65ED-4288-9D11-90A18C3BBAF4}">
   <dimension ref="A1:P13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="7.28515625" customWidth="1"/>
-    <col min="4" max="11" width="11.5703125" customWidth="1"/>
-    <col min="12" max="12" width="17.85546875" customWidth="1"/>
-    <col min="13" max="13" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" customWidth="1"/>
+    <col min="4" max="11" width="11.5546875" customWidth="1"/>
+    <col min="12" max="12" width="17.88671875" customWidth="1"/>
+    <col min="13" max="13" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
@@ -617,7 +626,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -669,7 +678,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -714,7 +723,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -766,7 +775,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -818,7 +827,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
@@ -863,7 +872,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -908,7 +917,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -956,7 +965,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -1004,7 +1013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -1049,7 +1058,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -1097,7 +1106,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
@@ -1114,8 +1123,8 @@
       <c r="E12" s="1">
         <v>4448</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>24</v>
+      <c r="F12" s="6">
+        <v>2124</v>
       </c>
       <c r="G12" s="1">
         <v>450</v>
@@ -1145,7 +1154,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -1162,8 +1171,8 @@
       <c r="E13" s="1">
         <v>50596</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>24</v>
+      <c r="F13" s="6">
+        <v>2124</v>
       </c>
       <c r="G13" s="1">
         <v>450</v>

--- a/subsystems database.xlsx
+++ b/subsystems database.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63B9E34-114B-4DFB-8C8F-8C4BB93820D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56CA8AB-DF65-450D-9509-41683BE5858F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DA27C19A-18DB-4E19-9AD3-8F88A97C8EE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Feuil1!$W$2:$W$32</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,8 +38,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="66">
   <si>
     <t>md</t>
   </si>
@@ -123,16 +148,134 @@
   </si>
   <si>
     <t>mt</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>0503-CE&amp;R-3</t>
+  </si>
+  <si>
+    <t>heat rejection</t>
+  </si>
+  <si>
+    <t>0503-CE&amp;R-6</t>
+  </si>
+  <si>
+    <t>0507-ESAS-A</t>
+  </si>
+  <si>
+    <t>0507-ESAS-B</t>
+  </si>
+  <si>
+    <t>minert</t>
+  </si>
+  <si>
+    <t>descent stage also performs LOI</t>
+  </si>
+  <si>
+    <t>reusable</t>
+  </si>
+  <si>
+    <t>0507-ESAS-C</t>
+  </si>
+  <si>
+    <t>0507-ESAS-E</t>
+  </si>
+  <si>
+    <t>0507-ESAS-G</t>
+  </si>
+  <si>
+    <t>0605-LLPS-LaRC-1A</t>
+  </si>
+  <si>
+    <t>0605-LLPS-LaRC-1B</t>
+  </si>
+  <si>
+    <t>0605-LLPS-LaRC-1C</t>
+  </si>
+  <si>
+    <t>0605-LLPS-LaRC-1D</t>
+  </si>
+  <si>
+    <t>0605-LLPS-LaRC-1E</t>
+  </si>
+  <si>
+    <t>0605-LLPS-LaRC-1F</t>
+  </si>
+  <si>
+    <t>descent stage also performs LOI, probable Isp for the LOX methan</t>
+  </si>
+  <si>
+    <t>0605-LLPS-LaRC-1G</t>
+  </si>
+  <si>
+    <t>0605-LLPS-LaRC-1H</t>
+  </si>
+  <si>
+    <t>lander performs LOI</t>
+  </si>
+  <si>
+    <t>0605-LLPS-LaRC-2</t>
+  </si>
+  <si>
+    <t>0605-LLPS-LaRC-3</t>
+  </si>
+  <si>
+    <t>0605-LLPS-GFSC-1</t>
+  </si>
+  <si>
+    <t>0605-LLPS-GSFC-3</t>
+  </si>
+  <si>
+    <t>0605-LLPS-1GSFC-4</t>
+  </si>
+  <si>
+    <t>skycrane</t>
+  </si>
+  <si>
+    <t>0605-LLPS-JSC-6</t>
+  </si>
+  <si>
+    <t>0605-LLPS-MSFC-1</t>
+  </si>
+  <si>
+    <t>0605-LLPS-MSFC-2</t>
+  </si>
+  <si>
+    <t>0605-LLPS-MSFC-3</t>
+  </si>
+  <si>
+    <t>0605-LLPS-MSFC-4</t>
+  </si>
+  <si>
+    <t>0605-LLPS-MSFC-6</t>
+  </si>
+  <si>
+    <t>0609-LLPS-GSFC</t>
+  </si>
+  <si>
+    <t>0609-LLPS-JSC-sortie</t>
+  </si>
+  <si>
+    <t>0609-LLPS-GRC-phase</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -152,7 +295,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -206,11 +349,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -228,6 +391,42 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -564,19 +763,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66EAA883-65ED-4288-9D11-90A18C3BBAF4}">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:W47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="7.33203125" customWidth="1"/>
-    <col min="4" max="11" width="11.5546875" customWidth="1"/>
-    <col min="12" max="12" width="17.88671875" customWidth="1"/>
-    <col min="13" max="13" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="12" width="11.5546875" customWidth="1"/>
+    <col min="13" max="13" width="17.88671875" customWidth="1"/>
+    <col min="14" max="14" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
@@ -593,40 +792,49 @@
         <v>2</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -643,47 +851,57 @@
       <c r="E2" s="1">
         <v>8780</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="6">
+        <f>B2-E2</f>
+        <v>7668</v>
+      </c>
+      <c r="G2" s="14">
         <v>2265</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>311</v>
       </c>
-      <c r="H2" s="4">
+      <c r="I2" s="4">
         <v>460</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2" s="1">
         <v>495</v>
       </c>
-      <c r="J2" s="1">
+      <c r="K2" s="1">
         <v>366</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>29</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="1">
         <v>404</v>
       </c>
-      <c r="M2" s="1">
+      <c r="N2" s="1">
         <v>273</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="1">
+      <c r="P2" s="1">
         <v>0.112</v>
       </c>
-      <c r="P2">
-        <f>O2*75</f>
+      <c r="Q2" s="1">
+        <f>P2*75</f>
         <v>8.4</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="W2" cm="1">
+        <f t="array" ref="W2:W32">SQRT(B2:B32)</f>
+        <v>128.24975633505119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B13" si="0">SUM(C3:E3)</f>
+        <f t="shared" ref="B3:B12" si="0">SUM(C3:E3)</f>
         <v>5038.6000000000004</v>
       </c>
       <c r="C3" s="1">
@@ -695,35 +913,46 @@
       <c r="E3" s="1">
         <v>2891.6000000000004</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="6">
+        <f t="shared" ref="F3:F39" si="1">B3-E3</f>
+        <v>2147</v>
+      </c>
+      <c r="G3" s="14">
         <v>1822</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1">
         <v>333</v>
       </c>
-      <c r="H3" s="4">
+      <c r="I3" s="4">
         <v>532.9</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>252.5</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K3" s="1">
         <v>125.7</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>120.1</v>
       </c>
-      <c r="L3" s="1">
+      <c r="M3" s="1">
         <v>113.5</v>
       </c>
-      <c r="M3" s="1">
+      <c r="N3" s="1">
         <v>56</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="W3">
+        <v>70.983096579396985</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -740,42 +969,51 @@
       <c r="E4" s="1">
         <v>25252</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="6">
+        <f t="shared" si="1"/>
+        <v>34823</v>
+      </c>
+      <c r="G4" s="14">
         <v>2100</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <v>450</v>
       </c>
-      <c r="H4" s="4">
+      <c r="I4" s="4">
         <v>1681</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
         <v>4258</v>
       </c>
-      <c r="J4" s="1">
+      <c r="K4" s="1">
         <v>478</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>934</v>
       </c>
-      <c r="L4" s="1">
+      <c r="M4" s="1">
         <v>2017</v>
       </c>
-      <c r="M4" s="1">
+      <c r="N4" s="1">
         <v>455</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O4" s="1">
+      <c r="P4" s="1">
         <v>2</v>
       </c>
-      <c r="P4">
-        <f>O4*3*24</f>
+      <c r="Q4" s="1">
+        <f>P4*3*24</f>
         <v>144</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="W4">
+        <v>245.10201957552289</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -792,42 +1030,51 @@
       <c r="E5" s="1">
         <v>36399</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="6">
+        <f t="shared" si="1"/>
+        <v>32899</v>
+      </c>
+      <c r="G5" s="14">
         <v>2100</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>333</v>
       </c>
-      <c r="H5" s="4">
+      <c r="I5" s="4">
         <v>1955</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <v>2943</v>
       </c>
-      <c r="J5" s="1">
+      <c r="K5" s="1">
         <v>478</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>1062</v>
       </c>
-      <c r="L5" s="1">
+      <c r="M5" s="1">
         <v>1006</v>
       </c>
-      <c r="M5" s="1">
+      <c r="N5" s="1">
         <v>455</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O5" s="1">
+      <c r="P5" s="1">
         <v>2</v>
       </c>
-      <c r="P5">
-        <f>O5*3*24</f>
+      <c r="Q5" s="1">
+        <f>P5*3*24</f>
         <v>144</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="W5">
+        <v>263.24513290847375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
@@ -844,35 +1091,46 @@
       <c r="E6" s="1">
         <v>44151</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="6">
+        <f t="shared" si="1"/>
+        <v>45214</v>
+      </c>
+      <c r="G6" s="14">
         <v>3100</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>450</v>
       </c>
-      <c r="H6" s="4">
+      <c r="I6" s="4">
         <v>1770</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>4969</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>385</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>307</v>
       </c>
-      <c r="L6" s="1">
+      <c r="M6" s="1">
         <v>420</v>
       </c>
-      <c r="M6" s="1">
+      <c r="N6" s="1">
         <v>1469</v>
       </c>
-      <c r="N6" s="1">
+      <c r="O6" s="1">
         <v>1878</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="W6">
+        <v>298.93979326948096</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -889,35 +1147,46 @@
       <c r="E7" s="1">
         <v>22502</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="6">
+        <f t="shared" si="1"/>
+        <v>22319</v>
+      </c>
+      <c r="G7" s="14">
         <v>2260</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>379</v>
       </c>
-      <c r="H7" s="4">
+      <c r="I7" s="4">
         <v>2822</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>1749</v>
       </c>
-      <c r="J7" s="1">
+      <c r="K7" s="1">
         <v>204</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>818</v>
       </c>
-      <c r="L7" s="1">
+      <c r="M7" s="1">
         <v>265</v>
       </c>
-      <c r="M7" s="1">
+      <c r="N7" s="1">
         <v>1</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="O7" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="W7">
+        <v>211.70970691019343</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -934,38 +1203,48 @@
       <c r="E8" s="1">
         <v>25486</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="6">
+        <f t="shared" si="1"/>
+        <v>36017</v>
+      </c>
+      <c r="G8" s="14">
         <v>1900</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>362</v>
       </c>
-      <c r="H8" s="4">
+      <c r="I8" s="4">
         <v>2015</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>2425</v>
       </c>
-      <c r="J8" s="1">
+      <c r="K8" s="1">
         <v>553</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>594</v>
       </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
         <v>1072</v>
       </c>
-      <c r="M8" s="1">
+      <c r="N8" s="1">
         <v>883</v>
       </c>
-      <c r="N8" s="1">
+      <c r="O8" s="1">
         <v>1508</v>
       </c>
-      <c r="O8" s="1">
+      <c r="P8" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="W8">
+        <v>247.99798386277257</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -982,38 +1261,48 @@
       <c r="E9" s="1">
         <v>23833</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="6">
+        <f t="shared" si="1"/>
+        <v>33787</v>
+      </c>
+      <c r="G9" s="14">
         <v>1900</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>351</v>
       </c>
-      <c r="H9" s="4">
+      <c r="I9" s="4">
         <v>1985</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>2347</v>
       </c>
-      <c r="J9" s="1">
+      <c r="K9" s="1">
         <v>553</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>594</v>
       </c>
-      <c r="L9" s="1">
+      <c r="M9" s="1">
         <v>1066</v>
       </c>
-      <c r="M9" s="1">
+      <c r="N9" s="1">
         <v>867</v>
       </c>
-      <c r="N9" s="1">
+      <c r="O9" s="1">
         <v>1483</v>
       </c>
-      <c r="O9" s="1">
+      <c r="P9" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="W9">
+        <v>240.04166305039632</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -1030,35 +1319,46 @@
       <c r="E10" s="1">
         <v>19152</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="6">
+        <f t="shared" si="1"/>
+        <v>27998</v>
+      </c>
+      <c r="G10" s="14">
         <v>1900</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>363</v>
       </c>
-      <c r="H10" s="4">
+      <c r="I10" s="4">
         <v>1877</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>1125</v>
       </c>
-      <c r="J10" s="1">
+      <c r="K10" s="1">
         <v>553</v>
       </c>
-      <c r="K10" s="1">
+      <c r="L10" s="1">
         <v>594</v>
       </c>
-      <c r="L10" s="1">
+      <c r="M10" s="1">
         <v>1049</v>
       </c>
-      <c r="M10" s="1">
+      <c r="N10" s="1">
         <v>772</v>
       </c>
-      <c r="N10" s="1">
+      <c r="O10" s="1">
         <v>1194</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="W10">
+        <v>217.14050750608465</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -1075,38 +1375,48 @@
       <c r="E11" s="1">
         <v>18312</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="6">
+        <f t="shared" si="1"/>
+        <v>26868</v>
+      </c>
+      <c r="G11" s="14">
         <v>1900</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>363</v>
       </c>
-      <c r="H11" s="4">
+      <c r="I11" s="4">
         <v>1860</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11" s="1">
         <v>1095</v>
       </c>
-      <c r="J11" s="1">
+      <c r="K11" s="1">
         <v>553</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>594</v>
       </c>
-      <c r="L11" s="1">
+      <c r="M11" s="1">
         <v>1046</v>
       </c>
-      <c r="M11" s="1">
+      <c r="N11" s="1">
         <v>764</v>
       </c>
-      <c r="N11" s="1">
+      <c r="O11" s="1">
         <v>1182</v>
       </c>
-      <c r="O11" s="1">
+      <c r="P11" s="1">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="W11">
+        <v>212.55587500702021</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
@@ -1124,87 +1434,1906 @@
         <v>4448</v>
       </c>
       <c r="F12" s="6">
-        <v>2124</v>
-      </c>
-      <c r="G12" s="1">
+        <f t="shared" si="1"/>
+        <v>6732</v>
+      </c>
+      <c r="G12" s="10">
+        <f>H12*9.81*(LN(B12/(F12)))</f>
+        <v>2239.2736279282085</v>
+      </c>
+      <c r="H12" s="1">
         <v>450</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="4">
         <v>1186.3399999999999</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12" s="1">
         <v>918.21</v>
       </c>
-      <c r="J12" s="1">
+      <c r="K12" s="1">
         <v>663</v>
       </c>
-      <c r="K12" s="1">
+      <c r="L12" s="1">
         <v>258.7</v>
       </c>
-      <c r="L12" s="1">
+      <c r="M12" s="1">
         <v>459.04</v>
       </c>
-      <c r="M12" s="1">
+      <c r="N12" s="1">
         <v>1</v>
       </c>
-      <c r="N12" s="1">
+      <c r="O12" s="1">
         <v>472</v>
       </c>
-      <c r="O12" s="1">
+      <c r="P12" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="W12">
+        <v>105.73551910309043</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B13" s="1">
-        <f t="shared" si="0"/>
-        <v>83417</v>
+        <f>45000+7853</f>
+        <v>52853</v>
       </c>
       <c r="C13" s="1">
-        <v>10747</v>
+        <f>5848+1862+119</f>
+        <v>7829</v>
       </c>
       <c r="D13" s="1">
+        <f>7853+14221</f>
         <v>22074</v>
       </c>
       <c r="E13" s="1">
-        <v>50596</v>
+        <v>22950</v>
       </c>
       <c r="F13" s="6">
-        <v>2124</v>
-      </c>
-      <c r="G13" s="1">
+        <f t="shared" si="1"/>
+        <v>29903</v>
+      </c>
+      <c r="G13" s="10">
+        <f>H13*9.81*(LN(B13/(F13)))</f>
+        <v>2514.3034845604184</v>
+      </c>
+      <c r="H13" s="1">
         <v>450</v>
       </c>
-      <c r="H13" s="1">
+      <c r="I13" s="4">
         <v>453</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13" s="1">
         <v>2969</v>
       </c>
-      <c r="J13" s="1">
+      <c r="K13" s="1">
         <v>288</v>
       </c>
-      <c r="K13" s="1">
+      <c r="L13" s="1">
         <v>519</v>
       </c>
-      <c r="L13" s="1">
+      <c r="M13" s="1">
         <v>56</v>
       </c>
-      <c r="M13" s="1">
+      <c r="N13" s="1">
         <v>527</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="O13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O13" s="1">
+      <c r="P13" s="1">
         <v>3</v>
       </c>
-      <c r="P13">
-        <f>O13*8.3</f>
+      <c r="Q13" s="1">
+        <f>P13*8.3</f>
         <v>24.900000000000002</v>
       </c>
+      <c r="R13" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="S13" s="1"/>
+      <c r="W13">
+        <v>229.8978033822855</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="9">
+        <f>5038-98-42.8</f>
+        <v>4897.2</v>
+      </c>
+      <c r="C14" s="9">
+        <v>1200.7</v>
+      </c>
+      <c r="D14" s="9">
+        <f>423.3+50</f>
+        <v>473.3</v>
+      </c>
+      <c r="E14" s="9">
+        <v>3223.8</v>
+      </c>
+      <c r="F14" s="6">
+        <f t="shared" si="1"/>
+        <v>1673.3999999999996</v>
+      </c>
+      <c r="G14" s="15">
+        <v>1910</v>
+      </c>
+      <c r="H14" s="9">
+        <v>353</v>
+      </c>
+      <c r="I14" s="11">
+        <v>404.8</v>
+      </c>
+      <c r="J14" s="9">
+        <v>252.5</v>
+      </c>
+      <c r="K14" s="9">
+        <v>125.7</v>
+      </c>
+      <c r="L14" s="9">
+        <v>120.1</v>
+      </c>
+      <c r="M14" s="16">
+        <v>113.5</v>
+      </c>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="W14">
+        <v>69.979997142040517</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="8">
+        <f>36272+18325</f>
+        <v>54597</v>
+      </c>
+      <c r="C15" s="8">
+        <v>6692</v>
+      </c>
+      <c r="D15" s="8">
+        <v>18325</v>
+      </c>
+      <c r="E15" s="8">
+        <v>29580</v>
+      </c>
+      <c r="F15" s="6">
+        <f t="shared" si="1"/>
+        <v>25017</v>
+      </c>
+      <c r="G15" s="10">
+        <f>H15*9.81*(LN(B15/(F15)))</f>
+        <v>2771.4549820453913</v>
+      </c>
+      <c r="H15" s="7">
+        <v>362</v>
+      </c>
+      <c r="I15" s="4">
+        <v>3757</v>
+      </c>
+      <c r="J15" s="8">
+        <v>1219</v>
+      </c>
+      <c r="K15" s="8">
+        <v>400</v>
+      </c>
+      <c r="L15" s="8">
+        <v>200</v>
+      </c>
+      <c r="M15" s="7">
+        <v>0</v>
+      </c>
+      <c r="N15" s="8">
+        <v>166</v>
+      </c>
+      <c r="O15" s="8">
+        <v>0</v>
+      </c>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="8"/>
+      <c r="S15" s="1"/>
+      <c r="W15">
+        <v>233.66000941538968</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="1">
+        <v>27021</v>
+      </c>
+      <c r="C16" s="1">
+        <f>5663+563+782</f>
+        <v>7008</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="1">
+        <v>20013</v>
+      </c>
+      <c r="F16" s="6">
+        <f t="shared" si="1"/>
+        <v>7008</v>
+      </c>
+      <c r="G16" s="10">
+        <f>H16*9.81*(LN(B16/(F16)))</f>
+        <v>4792.5915224416285</v>
+      </c>
+      <c r="H16" s="1">
+        <v>362</v>
+      </c>
+      <c r="I16" s="4">
+        <v>2441</v>
+      </c>
+      <c r="J16" s="1">
+        <v>983</v>
+      </c>
+      <c r="K16" s="1">
+        <v>741</v>
+      </c>
+      <c r="L16" s="1">
+        <v>65</v>
+      </c>
+      <c r="M16" s="1">
+        <f>57+564</f>
+        <v>621</v>
+      </c>
+      <c r="N16" s="1">
+        <v>109</v>
+      </c>
+      <c r="O16" s="1">
+        <v>703</v>
+      </c>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W16">
+        <v>164.38065579623412</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="1">
+        <f>35054+10808</f>
+        <v>45862</v>
+      </c>
+      <c r="C17" s="1">
+        <f>6136+1033+486</f>
+        <v>7655</v>
+      </c>
+      <c r="D17" s="1">
+        <f>10808+2294</f>
+        <v>13102</v>
+      </c>
+      <c r="E17" s="1">
+        <v>25105</v>
+      </c>
+      <c r="F17" s="6">
+        <f t="shared" si="1"/>
+        <v>20757</v>
+      </c>
+      <c r="G17" s="10">
+        <f>H17*9.81*(LN(B17/(F17)))</f>
+        <v>3499.6096559997736</v>
+      </c>
+      <c r="H17" s="1">
+        <v>450</v>
+      </c>
+      <c r="I17" s="4">
+        <v>1113</v>
+      </c>
+      <c r="J17" s="1">
+        <v>2632</v>
+      </c>
+      <c r="K17" s="1">
+        <v>468</v>
+      </c>
+      <c r="L17" s="1">
+        <v>69</v>
+      </c>
+      <c r="M17" s="1">
+        <f>281+88</f>
+        <v>369</v>
+      </c>
+      <c r="N17" s="1">
+        <v>842</v>
+      </c>
+      <c r="O17" s="1">
+        <v>1023</v>
+      </c>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W17">
+        <v>214.15415008820165</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="1">
+        <f>10790+39791+31330</f>
+        <v>81911</v>
+      </c>
+      <c r="C18" s="1">
+        <f>9226+500+148</f>
+        <v>9874</v>
+      </c>
+      <c r="D18" s="1">
+        <f>31330+10790</f>
+        <v>42120</v>
+      </c>
+      <c r="E18" s="1">
+        <v>29756</v>
+      </c>
+      <c r="F18" s="6">
+        <f t="shared" si="1"/>
+        <v>52155</v>
+      </c>
+      <c r="G18" s="10">
+        <f>H18*9.81*(LN(B18/(F18)))</f>
+        <v>1992.76373847382</v>
+      </c>
+      <c r="H18" s="1">
+        <v>450</v>
+      </c>
+      <c r="I18" s="4">
+        <v>2432</v>
+      </c>
+      <c r="J18" s="1">
+        <v>1826</v>
+      </c>
+      <c r="K18" s="1">
+        <v>336</v>
+      </c>
+      <c r="L18" s="1">
+        <v>145</v>
+      </c>
+      <c r="M18" s="1">
+        <f>1008+160</f>
+        <v>1168</v>
+      </c>
+      <c r="N18" s="1">
+        <v>1781</v>
+      </c>
+      <c r="O18" s="1">
+        <v>1538</v>
+      </c>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="W18">
+        <v>286.20097833515524</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="1">
+        <v>37494</v>
+      </c>
+      <c r="C19" s="1">
+        <v>9050</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="1">
+        <v>25486</v>
+      </c>
+      <c r="F19" s="6">
+        <f t="shared" si="1"/>
+        <v>12008</v>
+      </c>
+      <c r="G19" s="10">
+        <f>H19*9.81*(LN(B19/(F19)))</f>
+        <v>4043.4468832931575</v>
+      </c>
+      <c r="H19" s="1">
+        <v>362</v>
+      </c>
+      <c r="I19" s="4">
+        <v>2015</v>
+      </c>
+      <c r="J19" s="1">
+        <v>2425</v>
+      </c>
+      <c r="K19" s="1">
+        <v>553</v>
+      </c>
+      <c r="L19" s="1">
+        <v>594</v>
+      </c>
+      <c r="M19" s="1">
+        <f>777+295</f>
+        <v>1072</v>
+      </c>
+      <c r="N19" s="1">
+        <v>883</v>
+      </c>
+      <c r="O19" s="1">
+        <v>1508</v>
+      </c>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W19">
+        <v>193.63367475725909</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="1">
+        <v>35667</v>
+      </c>
+      <c r="C20" s="1">
+        <v>8895</v>
+      </c>
+      <c r="D20" s="6"/>
+      <c r="E20" s="1">
+        <v>23883</v>
+      </c>
+      <c r="F20" s="6">
+        <f t="shared" si="1"/>
+        <v>11784</v>
+      </c>
+      <c r="G20" s="10">
+        <f>H20*9.81*(LN(B20/(F20)))</f>
+        <v>3813.4080200345998</v>
+      </c>
+      <c r="H20" s="1">
+        <v>351</v>
+      </c>
+      <c r="I20" s="4">
+        <v>1985</v>
+      </c>
+      <c r="J20" s="1">
+        <v>2347</v>
+      </c>
+      <c r="K20" s="1">
+        <v>553</v>
+      </c>
+      <c r="L20" s="1">
+        <v>594</v>
+      </c>
+      <c r="M20" s="1">
+        <f>777+289</f>
+        <v>1066</v>
+      </c>
+      <c r="N20" s="1">
+        <v>867</v>
+      </c>
+      <c r="O20" s="1">
+        <v>1483</v>
+      </c>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W20">
+        <v>188.8570888264457</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="1">
+        <v>28819</v>
+      </c>
+      <c r="C21" s="1">
+        <f>7164+1286</f>
+        <v>8450</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="1">
+        <v>19152</v>
+      </c>
+      <c r="F21" s="6">
+        <f t="shared" si="1"/>
+        <v>9667</v>
+      </c>
+      <c r="G21" s="10">
+        <f>H21*9.81*(LN(B21/(F21)))</f>
+        <v>3889.7731377381924</v>
+      </c>
+      <c r="H21" s="1">
+        <v>363</v>
+      </c>
+      <c r="I21" s="4">
+        <v>1877</v>
+      </c>
+      <c r="J21" s="1">
+        <v>1125</v>
+      </c>
+      <c r="K21" s="1">
+        <v>553</v>
+      </c>
+      <c r="L21" s="1">
+        <v>594</v>
+      </c>
+      <c r="M21" s="1">
+        <f>777+272</f>
+        <v>1049</v>
+      </c>
+      <c r="N21" s="1">
+        <v>772</v>
+      </c>
+      <c r="O21" s="1">
+        <v>1194</v>
+      </c>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W21">
+        <v>169.7615975419647</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="1">
+        <f>34504+7755</f>
+        <v>42259</v>
+      </c>
+      <c r="C22" s="1">
+        <f>4722+95</f>
+        <v>4817</v>
+      </c>
+      <c r="D22" s="1">
+        <f>7755+1590</f>
+        <v>9345</v>
+      </c>
+      <c r="E22" s="1">
+        <v>27442</v>
+      </c>
+      <c r="F22" s="6">
+        <f t="shared" si="1"/>
+        <v>14817</v>
+      </c>
+      <c r="G22" s="10">
+        <f>H22*9.81*(LN(B22/(F22)))</f>
+        <v>3320.8578885135848</v>
+      </c>
+      <c r="H22" s="1">
+        <v>323</v>
+      </c>
+      <c r="I22" s="4">
+        <v>1101</v>
+      </c>
+      <c r="J22" s="1">
+        <v>1616</v>
+      </c>
+      <c r="K22" s="1">
+        <v>306</v>
+      </c>
+      <c r="L22" s="1">
+        <v>69</v>
+      </c>
+      <c r="M22" s="1">
+        <f>999+156</f>
+        <v>1155</v>
+      </c>
+      <c r="N22" s="1">
+        <f>842</f>
+        <v>842</v>
+      </c>
+      <c r="O22" s="1">
+        <f>1257</f>
+        <v>1257</v>
+      </c>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W22">
+        <v>205.56993943667931</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="1">
+        <f>34018+7812</f>
+        <v>41830</v>
+      </c>
+      <c r="C23" s="1">
+        <f>5621+1968</f>
+        <v>7589</v>
+      </c>
+      <c r="D23" s="1">
+        <f>7812+1590</f>
+        <v>9402</v>
+      </c>
+      <c r="E23" s="1">
+        <v>24744</v>
+      </c>
+      <c r="F23" s="6">
+        <f t="shared" si="1"/>
+        <v>17086</v>
+      </c>
+      <c r="G23" s="10">
+        <f>H23*9.81*(LN(B23/(F23)))</f>
+        <v>3188.3837747817079</v>
+      </c>
+      <c r="H23" s="6">
+        <v>363</v>
+      </c>
+      <c r="I23" s="4">
+        <v>1355</v>
+      </c>
+      <c r="J23" s="1">
+        <v>2013</v>
+      </c>
+      <c r="K23" s="1">
+        <v>306</v>
+      </c>
+      <c r="L23" s="1">
+        <v>69</v>
+      </c>
+      <c r="M23" s="1">
+        <f>124+141</f>
+        <v>265</v>
+      </c>
+      <c r="N23" s="1">
+        <f>584</f>
+        <v>584</v>
+      </c>
+      <c r="O23" s="1">
+        <f>937</f>
+        <v>937</v>
+      </c>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W23">
+        <v>204.52383724153034</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="1">
+        <f>15154+7737</f>
+        <v>22891</v>
+      </c>
+      <c r="C24" s="1">
+        <f>2761</f>
+        <v>2761</v>
+      </c>
+      <c r="D24" s="1">
+        <f>7737+1590</f>
+        <v>9327</v>
+      </c>
+      <c r="E24" s="1">
+        <f>10458</f>
+        <v>10458</v>
+      </c>
+      <c r="F24" s="6">
+        <f t="shared" si="1"/>
+        <v>12433</v>
+      </c>
+      <c r="G24" s="10">
+        <f>H24*9.81*(LN(B24/(F24)))</f>
+        <v>1934.0987736564762</v>
+      </c>
+      <c r="H24" s="1">
+        <v>323</v>
+      </c>
+      <c r="I24" s="4">
+        <v>451</v>
+      </c>
+      <c r="J24" s="1">
+        <v>677</v>
+      </c>
+      <c r="K24" s="1">
+        <v>306</v>
+      </c>
+      <c r="L24" s="1">
+        <v>69</v>
+      </c>
+      <c r="M24" s="1">
+        <f>124+86</f>
+        <v>210</v>
+      </c>
+      <c r="N24" s="1">
+        <v>496</v>
+      </c>
+      <c r="O24" s="1">
+        <v>460</v>
+      </c>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="W24">
+        <v>151.29771974487917</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="1">
+        <f>15472+7667</f>
+        <v>23139</v>
+      </c>
+      <c r="C25" s="1">
+        <v>3442</v>
+      </c>
+      <c r="D25" s="1">
+        <f>7667+1590</f>
+        <v>9257</v>
+      </c>
+      <c r="E25" s="1">
+        <v>9350</v>
+      </c>
+      <c r="F25" s="6">
+        <f t="shared" si="1"/>
+        <v>13789</v>
+      </c>
+      <c r="G25" s="10">
+        <f>H25*9.81*(LN(B25/(F25)))</f>
+        <v>1843.3612424096523</v>
+      </c>
+      <c r="H25" s="6">
+        <v>363</v>
+      </c>
+      <c r="I25" s="4">
+        <v>717</v>
+      </c>
+      <c r="J25" s="1">
+        <v>955</v>
+      </c>
+      <c r="K25" s="1">
+        <v>306</v>
+      </c>
+      <c r="L25" s="1">
+        <v>69</v>
+      </c>
+      <c r="M25" s="1">
+        <f>124+95</f>
+        <v>219</v>
+      </c>
+      <c r="N25" s="1">
+        <v>510</v>
+      </c>
+      <c r="O25" s="1">
+        <v>574</v>
+      </c>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="W25">
+        <v>152.11508800904662</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="1">
+        <f>13564+9600</f>
+        <v>23164</v>
+      </c>
+      <c r="C26" s="1">
+        <f>2761+250</f>
+        <v>3011</v>
+      </c>
+      <c r="D26" s="1">
+        <v>9600</v>
+      </c>
+      <c r="E26" s="1">
+        <v>10458</v>
+      </c>
+      <c r="F26" s="6">
+        <f t="shared" si="1"/>
+        <v>12706</v>
+      </c>
+      <c r="G26" s="10">
+        <f>H26*9.81*(LN(B26/(F26)))</f>
+        <v>1902.8416147795385</v>
+      </c>
+      <c r="H26" s="1">
+        <v>323</v>
+      </c>
+      <c r="I26" s="4">
+        <v>451</v>
+      </c>
+      <c r="J26" s="1">
+        <v>677</v>
+      </c>
+      <c r="K26" s="1">
+        <v>306</v>
+      </c>
+      <c r="L26" s="1">
+        <v>69</v>
+      </c>
+      <c r="M26" s="1">
+        <f>124+86</f>
+        <v>210</v>
+      </c>
+      <c r="N26" s="1">
+        <v>496</v>
+      </c>
+      <c r="O26" s="1">
+        <v>460</v>
+      </c>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="W26">
+        <v>152.19724044804491</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B27" s="1">
+        <f>13882+9313</f>
+        <v>23195</v>
+      </c>
+      <c r="C27" s="1">
+        <v>3442</v>
+      </c>
+      <c r="D27" s="1">
+        <v>9313</v>
+      </c>
+      <c r="E27" s="1">
+        <v>9350</v>
+      </c>
+      <c r="F27" s="6">
+        <f t="shared" si="1"/>
+        <v>13845</v>
+      </c>
+      <c r="G27" s="10">
+        <f>H27*9.81*(LN(B27/(F27)))</f>
+        <v>1837.5362833866116</v>
+      </c>
+      <c r="H27" s="6">
+        <v>363</v>
+      </c>
+      <c r="I27" s="4">
+        <v>717</v>
+      </c>
+      <c r="J27" s="1">
+        <v>955</v>
+      </c>
+      <c r="K27" s="1">
+        <v>306</v>
+      </c>
+      <c r="L27" s="1">
+        <v>69</v>
+      </c>
+      <c r="M27" s="1">
+        <f>124+95</f>
+        <v>219</v>
+      </c>
+      <c r="N27" s="1">
+        <v>510</v>
+      </c>
+      <c r="O27" s="1">
+        <v>574</v>
+      </c>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="W27">
+        <v>152.29904792873788</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="1">
+        <f>33067+14234</f>
+        <v>47301</v>
+      </c>
+      <c r="C28" s="1">
+        <f>4739+658</f>
+        <v>5397</v>
+      </c>
+      <c r="D28" s="1">
+        <v>14234</v>
+      </c>
+      <c r="E28" s="1">
+        <v>27575</v>
+      </c>
+      <c r="F28" s="6">
+        <f t="shared" si="1"/>
+        <v>19726</v>
+      </c>
+      <c r="G28" s="10">
+        <f>H28*9.81*(LN(B28/(F28)))</f>
+        <v>2771.2643882136222</v>
+      </c>
+      <c r="H28" s="1">
+        <v>323</v>
+      </c>
+      <c r="I28" s="4">
+        <v>1017</v>
+      </c>
+      <c r="J28" s="1">
+        <v>1624</v>
+      </c>
+      <c r="K28" s="1">
+        <v>306</v>
+      </c>
+      <c r="L28" s="1">
+        <v>69</v>
+      </c>
+      <c r="M28" s="1">
+        <f>124+162</f>
+        <v>286</v>
+      </c>
+      <c r="N28" s="1">
+        <v>555</v>
+      </c>
+      <c r="O28" s="1">
+        <v>790</v>
+      </c>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="W28">
+        <v>217.48793069961377</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="1">
+        <f>32700+14415</f>
+        <v>47115</v>
+      </c>
+      <c r="C29" s="1">
+        <f>5655+1981</f>
+        <v>7636</v>
+      </c>
+      <c r="D29" s="1">
+        <v>14415</v>
+      </c>
+      <c r="E29" s="1">
+        <v>24969</v>
+      </c>
+      <c r="F29" s="6">
+        <f t="shared" si="1"/>
+        <v>22146</v>
+      </c>
+      <c r="G29" s="10">
+        <f>H29*9.81*(LN(B29/(F29)))</f>
+        <v>2688.3445036070134</v>
+      </c>
+      <c r="H29" s="6">
+        <v>363</v>
+      </c>
+      <c r="I29" s="4">
+        <v>1364</v>
+      </c>
+      <c r="J29" s="1">
+        <v>2027</v>
+      </c>
+      <c r="K29" s="1">
+        <v>306</v>
+      </c>
+      <c r="L29" s="1">
+        <v>69</v>
+      </c>
+      <c r="M29" s="1">
+        <f>124+142</f>
+        <v>266</v>
+      </c>
+      <c r="N29" s="1">
+        <f>589</f>
+        <v>589</v>
+      </c>
+      <c r="O29" s="1">
+        <v>942</v>
+      </c>
+      <c r="P29" s="1"/>
+      <c r="S29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="W29">
+        <v>217.05989956691678</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="1">
+        <f>14030+5550</f>
+        <v>19580</v>
+      </c>
+      <c r="C30" s="1">
+        <f>4690+990</f>
+        <v>5680</v>
+      </c>
+      <c r="D30" s="1">
+        <f>5550+500</f>
+        <v>6050</v>
+      </c>
+      <c r="E30" s="1">
+        <f>6900</f>
+        <v>6900</v>
+      </c>
+      <c r="F30" s="6">
+        <f t="shared" si="1"/>
+        <v>12680</v>
+      </c>
+      <c r="G30" s="10">
+        <f>H30*9.81*(LN(B30/(F30)))</f>
+        <v>1960.6465782897556</v>
+      </c>
+      <c r="H30" s="1">
+        <v>460</v>
+      </c>
+      <c r="I30" s="4">
+        <v>1150</v>
+      </c>
+      <c r="J30" s="1">
+        <v>750</v>
+      </c>
+      <c r="K30" s="1">
+        <v>630</v>
+      </c>
+      <c r="L30" s="1">
+        <v>80</v>
+      </c>
+      <c r="M30" s="1">
+        <f>740+60</f>
+        <v>800</v>
+      </c>
+      <c r="N30" s="1">
+        <f>440</f>
+        <v>440</v>
+      </c>
+      <c r="O30" s="1">
+        <f>840</f>
+        <v>840</v>
+      </c>
+      <c r="P30" s="1"/>
+      <c r="W30">
+        <v>139.92855319769444</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="1">
+        <v>37848</v>
+      </c>
+      <c r="C31" s="1">
+        <f>9369+1885</f>
+        <v>11254</v>
+      </c>
+      <c r="D31" s="6"/>
+      <c r="E31" s="1">
+        <v>25492</v>
+      </c>
+      <c r="F31" s="6">
+        <f t="shared" si="1"/>
+        <v>12356</v>
+      </c>
+      <c r="G31" s="10">
+        <f t="shared" ref="G31:G39" si="2">H31*9.81*(LN(B31/(F31)))</f>
+        <v>3843.5847532961689</v>
+      </c>
+      <c r="H31" s="1">
+        <v>350</v>
+      </c>
+      <c r="I31" s="4">
+        <v>2464</v>
+      </c>
+      <c r="J31" s="1">
+        <v>2422</v>
+      </c>
+      <c r="K31" s="1">
+        <v>553</v>
+      </c>
+      <c r="L31" s="1">
+        <v>594</v>
+      </c>
+      <c r="M31" s="1">
+        <f>777+106</f>
+        <v>883</v>
+      </c>
+      <c r="N31" s="1">
+        <f>892</f>
+        <v>892</v>
+      </c>
+      <c r="O31" s="1">
+        <v>1561</v>
+      </c>
+      <c r="P31" s="1"/>
+      <c r="S31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W31">
+        <v>194.54562446891475</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="1">
+        <f>39807+5193</f>
+        <v>45000</v>
+      </c>
+      <c r="C32" s="1">
+        <v>8260</v>
+      </c>
+      <c r="D32" s="1">
+        <f>5193+4654</f>
+        <v>9847</v>
+      </c>
+      <c r="E32" s="1">
+        <f>24706</f>
+        <v>24706</v>
+      </c>
+      <c r="F32" s="6">
+        <f t="shared" si="1"/>
+        <v>20294</v>
+      </c>
+      <c r="G32" s="10">
+        <f t="shared" si="2"/>
+        <v>3023.2703425059144</v>
+      </c>
+      <c r="H32" s="17">
+        <v>387</v>
+      </c>
+      <c r="I32" s="4">
+        <v>1932</v>
+      </c>
+      <c r="J32" s="1">
+        <v>2239</v>
+      </c>
+      <c r="K32" s="1">
+        <v>468</v>
+      </c>
+      <c r="L32" s="1">
+        <v>306</v>
+      </c>
+      <c r="M32" s="1">
+        <f>1119+88</f>
+        <v>1207</v>
+      </c>
+      <c r="N32" s="1">
+        <v>640</v>
+      </c>
+      <c r="O32" s="1">
+        <v>1377</v>
+      </c>
+      <c r="P32" s="1"/>
+      <c r="W32">
+        <v>212.13203435596427</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="1">
+        <f>40007+4994</f>
+        <v>45001</v>
+      </c>
+      <c r="C33" s="1">
+        <f>8627+1502</f>
+        <v>10129</v>
+      </c>
+      <c r="D33" s="1">
+        <f>4994+686</f>
+        <v>5680</v>
+      </c>
+      <c r="E33" s="1">
+        <v>24706</v>
+      </c>
+      <c r="F33" s="6">
+        <f t="shared" si="1"/>
+        <v>20295</v>
+      </c>
+      <c r="G33" s="10">
+        <f t="shared" si="2"/>
+        <v>3023.1676386581948</v>
+      </c>
+      <c r="H33" s="17">
+        <v>387</v>
+      </c>
+      <c r="I33" s="4">
+        <v>2203</v>
+      </c>
+      <c r="J33" s="1">
+        <v>2239</v>
+      </c>
+      <c r="K33" s="1">
+        <v>468</v>
+      </c>
+      <c r="L33" s="1">
+        <v>306</v>
+      </c>
+      <c r="M33" s="1">
+        <f>1104+88</f>
+        <v>1192</v>
+      </c>
+      <c r="N33" s="1">
+        <v>690</v>
+      </c>
+      <c r="O33" s="1">
+        <v>1438</v>
+      </c>
+      <c r="P33" s="1"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="1">
+        <f>39779+5220</f>
+        <v>44999</v>
+      </c>
+      <c r="C34" s="1">
+        <f>8268+1583</f>
+        <v>9851</v>
+      </c>
+      <c r="D34" s="1">
+        <f>5220+4736</f>
+        <v>9956</v>
+      </c>
+      <c r="E34" s="1">
+        <v>24706</v>
+      </c>
+      <c r="F34" s="6">
+        <f t="shared" si="1"/>
+        <v>20293</v>
+      </c>
+      <c r="G34" s="10">
+        <f t="shared" si="2"/>
+        <v>3023.3730536970029</v>
+      </c>
+      <c r="H34" s="18">
+        <v>387</v>
+      </c>
+      <c r="I34" s="4">
+        <v>2289</v>
+      </c>
+      <c r="J34" s="1">
+        <v>2239</v>
+      </c>
+      <c r="K34" s="1">
+        <v>468</v>
+      </c>
+      <c r="L34" s="1">
+        <v>354</v>
+      </c>
+      <c r="M34" s="1">
+        <f>1104+88</f>
+        <v>1192</v>
+      </c>
+      <c r="N34" s="1">
+        <f>257</f>
+        <v>257</v>
+      </c>
+      <c r="O34" s="1">
+        <f>1378</f>
+        <v>1378</v>
+      </c>
+      <c r="P34" s="1"/>
+      <c r="S34" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" s="1">
+        <f>53643</f>
+        <v>53643</v>
+      </c>
+      <c r="C35" s="1">
+        <f>6753+1033</f>
+        <v>7786</v>
+      </c>
+      <c r="D35" s="1">
+        <v>19000</v>
+      </c>
+      <c r="E35" s="1">
+        <v>26371</v>
+      </c>
+      <c r="F35" s="6">
+        <f t="shared" si="1"/>
+        <v>27272</v>
+      </c>
+      <c r="G35" s="10">
+        <f t="shared" si="2"/>
+        <v>2986.3670934036945</v>
+      </c>
+      <c r="H35" s="1">
+        <v>450</v>
+      </c>
+      <c r="I35" s="4">
+        <v>1113</v>
+      </c>
+      <c r="J35" s="1">
+        <v>2362</v>
+      </c>
+      <c r="K35" s="1">
+        <v>468</v>
+      </c>
+      <c r="L35" s="1">
+        <v>69</v>
+      </c>
+      <c r="M35" s="1">
+        <f>281+88</f>
+        <v>369</v>
+      </c>
+      <c r="N35" s="1">
+        <v>640</v>
+      </c>
+      <c r="O35" s="1">
+        <v>1640</v>
+      </c>
+      <c r="P35" s="1"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B36" s="1">
+        <f>45001+4971</f>
+        <v>49972</v>
+      </c>
+      <c r="C36" s="1">
+        <f>11660+3671</f>
+        <v>15331</v>
+      </c>
+      <c r="D36" s="1">
+        <f>4971+1627</f>
+        <v>6598</v>
+      </c>
+      <c r="E36" s="1">
+        <f>28043</f>
+        <v>28043</v>
+      </c>
+      <c r="F36" s="6">
+        <f t="shared" si="1"/>
+        <v>21929</v>
+      </c>
+      <c r="G36" s="10">
+        <f t="shared" si="2"/>
+        <v>3636.0156688434217</v>
+      </c>
+      <c r="H36" s="1">
+        <v>450</v>
+      </c>
+      <c r="I36" s="4">
+        <v>4545</v>
+      </c>
+      <c r="J36" s="1">
+        <v>3111</v>
+      </c>
+      <c r="K36" s="1">
+        <v>934</v>
+      </c>
+      <c r="L36" s="1">
+        <v>441</v>
+      </c>
+      <c r="M36" s="1">
+        <f>156+180</f>
+        <v>336</v>
+      </c>
+      <c r="N36" s="1">
+        <f>946</f>
+        <v>946</v>
+      </c>
+      <c r="O36" s="1">
+        <v>1864</v>
+      </c>
+      <c r="P36" s="1"/>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B37" s="1">
+        <f>45001+4971</f>
+        <v>49972</v>
+      </c>
+      <c r="C37" s="1">
+        <f>11448+3671</f>
+        <v>15119</v>
+      </c>
+      <c r="D37" s="1">
+        <f>4971+1839</f>
+        <v>6810</v>
+      </c>
+      <c r="E37" s="1">
+        <f>28043</f>
+        <v>28043</v>
+      </c>
+      <c r="F37" s="6">
+        <f t="shared" si="1"/>
+        <v>21929</v>
+      </c>
+      <c r="G37" s="10">
+        <f t="shared" si="2"/>
+        <v>3636.0156688434217</v>
+      </c>
+      <c r="H37" s="1">
+        <v>450</v>
+      </c>
+      <c r="I37" s="4">
+        <v>4430</v>
+      </c>
+      <c r="J37" s="1">
+        <v>3182</v>
+      </c>
+      <c r="K37" s="1">
+        <v>934</v>
+      </c>
+      <c r="L37" s="1">
+        <v>441</v>
+      </c>
+      <c r="M37" s="1">
+        <f>156+180</f>
+        <v>336</v>
+      </c>
+      <c r="N37" s="1">
+        <v>429</v>
+      </c>
+      <c r="O37" s="1">
+        <v>1696</v>
+      </c>
+      <c r="P37" s="1"/>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" s="1">
+        <f>45000+5005</f>
+        <v>50005</v>
+      </c>
+      <c r="C38" s="1">
+        <f>16575+2445</f>
+        <v>19020</v>
+      </c>
+      <c r="D38" s="1">
+        <f>937+5005</f>
+        <v>5942</v>
+      </c>
+      <c r="E38" s="1">
+        <f>28043</f>
+        <v>28043</v>
+      </c>
+      <c r="F38" s="6">
+        <f t="shared" si="1"/>
+        <v>21962</v>
+      </c>
+      <c r="G38" s="10">
+        <f t="shared" si="2"/>
+        <v>3632.2917133551828</v>
+      </c>
+      <c r="H38" s="1">
+        <v>450</v>
+      </c>
+      <c r="I38" s="4">
+        <f>6565</f>
+        <v>6565</v>
+      </c>
+      <c r="J38" s="1">
+        <v>2889</v>
+      </c>
+      <c r="K38" s="1">
+        <v>934</v>
+      </c>
+      <c r="L38" s="1">
+        <v>441</v>
+      </c>
+      <c r="M38" s="1">
+        <f>156+180</f>
+        <v>336</v>
+      </c>
+      <c r="N38" s="1">
+        <f>446</f>
+        <v>446</v>
+      </c>
+      <c r="O38" s="1">
+        <v>1964</v>
+      </c>
+      <c r="P38" s="1"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" s="1">
+        <f>45000+4971</f>
+        <v>49971</v>
+      </c>
+      <c r="C39" s="1">
+        <f>8131+2889</f>
+        <v>11020</v>
+      </c>
+      <c r="D39" s="1">
+        <f>4971+5937</f>
+        <v>10908</v>
+      </c>
+      <c r="E39" s="1">
+        <f>28043</f>
+        <v>28043</v>
+      </c>
+      <c r="F39" s="6">
+        <f t="shared" si="1"/>
+        <v>21928</v>
+      </c>
+      <c r="G39" s="10">
+        <f t="shared" si="2"/>
+        <v>3636.1286418487784</v>
+      </c>
+      <c r="H39" s="1">
+        <v>450</v>
+      </c>
+      <c r="I39" s="4">
+        <v>1856</v>
+      </c>
+      <c r="J39" s="1">
+        <v>2578</v>
+      </c>
+      <c r="K39" s="1">
+        <v>934</v>
+      </c>
+      <c r="L39" s="1">
+        <v>441</v>
+      </c>
+      <c r="M39" s="1">
+        <f>156+180</f>
+        <v>336</v>
+      </c>
+      <c r="N39" s="1">
+        <v>706</v>
+      </c>
+      <c r="O39" s="1">
+        <v>1280</v>
+      </c>
+      <c r="P39" s="1"/>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" s="1">
+        <f>45001+4971</f>
+        <v>49972</v>
+      </c>
+      <c r="C40" s="1">
+        <f>7695+2731</f>
+        <v>10426</v>
+      </c>
+      <c r="D40" s="1">
+        <f>4971+6532</f>
+        <v>11503</v>
+      </c>
+      <c r="E40" s="1">
+        <v>28043</v>
+      </c>
+      <c r="F40" s="6">
+        <f t="shared" ref="F40:F43" si="3">B40-E40</f>
+        <v>21929</v>
+      </c>
+      <c r="G40" s="10">
+        <f t="shared" ref="G40:G43" si="4">H40*9.81*(LN(B40/(F40)))</f>
+        <v>3636.0156688434217</v>
+      </c>
+      <c r="H40" s="1">
+        <v>450</v>
+      </c>
+      <c r="I40" s="4">
+        <v>1638</v>
+      </c>
+      <c r="J40" s="1">
+        <v>2601</v>
+      </c>
+      <c r="K40" s="1">
+        <v>934</v>
+      </c>
+      <c r="L40" s="1">
+        <v>441</v>
+      </c>
+      <c r="M40" s="1">
+        <f>156+180</f>
+        <v>336</v>
+      </c>
+      <c r="N40" s="1">
+        <v>548</v>
+      </c>
+      <c r="O40" s="1">
+        <v>1197</v>
+      </c>
+      <c r="P40" s="1"/>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" s="1">
+        <f>6912</f>
+        <v>6912</v>
+      </c>
+      <c r="C41" s="1">
+        <f>3087</f>
+        <v>3087</v>
+      </c>
+      <c r="D41" s="6"/>
+      <c r="E41" s="1">
+        <f>3345</f>
+        <v>3345</v>
+      </c>
+      <c r="F41" s="6">
+        <f t="shared" si="3"/>
+        <v>3567</v>
+      </c>
+      <c r="G41" s="10">
+        <f t="shared" si="4"/>
+        <v>2096.1568748948289</v>
+      </c>
+      <c r="H41" s="1">
+        <v>323</v>
+      </c>
+      <c r="I41" s="4">
+        <v>1050</v>
+      </c>
+      <c r="J41" s="1">
+        <v>479</v>
+      </c>
+      <c r="K41" s="1">
+        <v>244</v>
+      </c>
+      <c r="L41" s="1">
+        <v>273</v>
+      </c>
+      <c r="M41" s="1">
+        <f>323+217</f>
+        <v>540</v>
+      </c>
+      <c r="N41" s="1">
+        <v>0</v>
+      </c>
+      <c r="O41" s="1">
+        <v>501</v>
+      </c>
+      <c r="P41" s="1"/>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B42" s="1">
+        <f>37668+6685</f>
+        <v>44353</v>
+      </c>
+      <c r="C42" s="1">
+        <f>11486</f>
+        <v>11486</v>
+      </c>
+      <c r="D42" s="1">
+        <v>6685</v>
+      </c>
+      <c r="E42" s="1">
+        <v>26182</v>
+      </c>
+      <c r="F42" s="1">
+        <f t="shared" si="3"/>
+        <v>18171</v>
+      </c>
+      <c r="G42" s="14">
+        <f t="shared" si="4"/>
+        <v>3939.2942323794919</v>
+      </c>
+      <c r="H42" s="1">
+        <v>450</v>
+      </c>
+      <c r="I42" s="4">
+        <v>4939</v>
+      </c>
+      <c r="J42" s="1">
+        <v>2352</v>
+      </c>
+      <c r="K42" s="1">
+        <v>1563</v>
+      </c>
+      <c r="L42" s="1">
+        <v>263</v>
+      </c>
+      <c r="M42" s="1">
+        <f>700+340</f>
+        <v>1040</v>
+      </c>
+      <c r="N42" s="1">
+        <v>1329</v>
+      </c>
+      <c r="O42" s="1">
+        <v>0</v>
+      </c>
+      <c r="P42" s="1"/>
+      <c r="S42" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B43" s="1">
+        <v>11652</v>
+      </c>
+      <c r="C43" s="1">
+        <f>6975+229</f>
+        <v>7204</v>
+      </c>
+      <c r="D43" s="6"/>
+      <c r="E43" s="1">
+        <v>4448</v>
+      </c>
+      <c r="F43" s="1">
+        <f t="shared" si="3"/>
+        <v>7204</v>
+      </c>
+      <c r="G43" s="14">
+        <f t="shared" si="4"/>
+        <v>2122.6744123181657</v>
+      </c>
+      <c r="H43" s="1">
+        <v>450</v>
+      </c>
+      <c r="I43" s="4">
+        <v>1564</v>
+      </c>
+      <c r="J43" s="1">
+        <v>1186</v>
+      </c>
+      <c r="K43" s="1">
+        <v>343</v>
+      </c>
+      <c r="L43" s="1">
+        <v>1453</v>
+      </c>
+      <c r="M43" s="1">
+        <f>473+0</f>
+        <v>473</v>
+      </c>
+      <c r="N43" s="1">
+        <v>1053</v>
+      </c>
+      <c r="O43" s="1">
+        <v>472</v>
+      </c>
+      <c r="P43" s="1"/>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/subsystems database.xlsx
+++ b/subsystems database.xlsx
@@ -1,23 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\EUCASS_2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56CA8AB-DF65-450D-9509-41683BE5858F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3641FB-E0FD-4EAA-BFCF-347059E7A783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DA27C19A-18DB-4E19-9AD3-8F88A97C8EE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Feuil1!$W$2:$W$32</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,8 +35,211 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Conall DE PAOR</author>
+  </authors>
+  <commentList>
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{B1A6C1CD-F490-4240-85E7-8856ED16E89B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Conall DE PAOR:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+other plus the "non-cargo" part
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{77A337B4-1EB3-48F2-B77C-067BA50FB2BF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Conall DE PAOR:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+adjustment to correct probable error in the source</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D15" authorId="0" shapeId="0" xr:uid="{0521C0D9-2090-4D0B-9C8E-0B13C1B1FE50}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall DE PAOR:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+just the cargo portion of manned lander. Mp is likely larger</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D18" authorId="0" shapeId="0" xr:uid="{B797AA45-199A-49F6-80C4-62523E20DF08}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall DE PAOR:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+just the cargo portion of the manned lander. Real mp is slighlty larger</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D19" authorId="0" shapeId="0" xr:uid="{EF7EFF7D-2E70-45A0-BBF9-079C8840FC8C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall DE PAOR:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+just the cargo portion of the manned lander. Real mp is slighlty larger</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D20" authorId="0" shapeId="0" xr:uid="{1D818EF2-060F-400B-B534-BEFEF5DA0F2D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall DE PAOR:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+just the cargo portion of the manned lander. Real mp is slighlty larger</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D31" authorId="0" shapeId="0" xr:uid="{7240658D-68CC-44CA-A59D-13B3F282DC16}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall DE PAOR:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+just the cargo portion of the manned lander. Real mp is slighlty larger</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D41" authorId="0" shapeId="0" xr:uid="{BE1A3CF6-BF67-4834-B5F3-08209098C5A8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall DE PAOR:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+listed cargo mass. Real payload capacity is likely higher</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -61,7 +261,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="69">
   <si>
     <t>md</t>
   </si>
@@ -132,15 +332,6 @@
     <t>9205-FLO-1-CLS</t>
   </si>
   <si>
-    <t>0609-LLPS-GRC</t>
-  </si>
-  <si>
-    <t>ND</t>
-  </si>
-  <si>
-    <t>0610-LAT-1</t>
-  </si>
-  <si>
     <t>kW</t>
   </si>
   <si>
@@ -259,13 +450,31 @@
   </si>
   <si>
     <t>0609-LLPS-GRC-phase</t>
+  </si>
+  <si>
+    <t>md_check</t>
+  </si>
+  <si>
+    <t>dv_check</t>
+  </si>
+  <si>
+    <t>delta</t>
+  </si>
+  <si>
+    <t>0609-LLPS-GRC-phase II</t>
+  </si>
+  <si>
+    <t>0610-LAT-3</t>
+  </si>
+  <si>
+    <t>0605-LLPS-LaRC-1i</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -280,8 +489,40 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -291,6 +532,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -373,7 +620,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -393,40 +640,47 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -762,8 +1016,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66EAA883-65ED-4288-9D11-90A18C3BBAF4}">
-  <dimension ref="A1:W47"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66EAA883-65ED-4288-9D11-90A18C3BBAF4}">
+  <dimension ref="A1:Z47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
@@ -775,12 +1029,12 @@
     <col min="15" max="15" width="6.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -792,172 +1046,211 @@
         <v>2</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="V1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="S1" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A2" s="16" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="1">
         <f>SUM(C2:E2)</f>
-        <v>16448</v>
+        <v>16194</v>
       </c>
       <c r="C2" s="1">
         <v>2373</v>
       </c>
       <c r="D2" s="1">
-        <v>5295</v>
+        <f>4795+499</f>
+        <v>5294</v>
       </c>
       <c r="E2" s="1">
-        <v>8780</v>
-      </c>
-      <c r="F2" s="6">
-        <f>B2-E2</f>
-        <v>7668</v>
-      </c>
-      <c r="G2" s="14">
+        <v>8527</v>
+      </c>
+      <c r="F2" s="1">
+        <f>SUM(C2:E2)-B2</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="6">
+        <f t="shared" ref="G2:G42" si="0">B2-E2</f>
+        <v>7667</v>
+      </c>
+      <c r="H2" s="11">
         <v>2265</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="11">
+        <f t="shared" ref="I2:I42" si="1">J2*9.81*(LN(B2/(G2)))</f>
+        <v>2281.2123870086598</v>
+      </c>
+      <c r="J2" s="1">
         <v>311</v>
       </c>
-      <c r="I2" s="4">
+      <c r="K2" s="4">
         <v>460</v>
       </c>
-      <c r="J2" s="1">
+      <c r="L2" s="1">
         <v>495</v>
       </c>
-      <c r="K2" s="1">
+      <c r="M2" s="1">
         <v>366</v>
       </c>
-      <c r="L2" s="1">
+      <c r="N2" s="1">
         <v>29</v>
       </c>
-      <c r="M2" s="1">
+      <c r="O2" s="1">
         <v>404</v>
       </c>
-      <c r="N2" s="1">
-        <v>273</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="P2" s="1">
+        <f>273+346</f>
+        <v>619</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>0</v>
+      </c>
+      <c r="R2" s="1">
+        <f t="shared" ref="R2:R42" si="2">SUM(K2:Q2)-C2</f>
+        <v>0</v>
+      </c>
+      <c r="S2" s="1">
         <v>0.112</v>
       </c>
-      <c r="Q2" s="1">
-        <f>P2*75</f>
+      <c r="T2" s="1">
+        <f>S2*75</f>
         <v>8.4</v>
       </c>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="W2" cm="1">
-        <f t="array" ref="W2:W32">SQRT(B2:B32)</f>
-        <v>128.24975633505119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="U2" s="1"/>
+      <c r="V2" s="15"/>
+      <c r="Z2" cm="1">
+        <f t="array" ref="Z2:Z32">SQRT(B2:B32)</f>
+        <v>127.25564820470642</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B12" si="0">SUM(C3:E3)</f>
+        <f t="shared" ref="B3:B5" si="3">SUM(C3:E3)</f>
         <v>5038.6000000000004</v>
       </c>
       <c r="C3" s="1">
-        <v>1673.7</v>
+        <f>1200.7-28.8</f>
+        <v>1171.9000000000001</v>
       </c>
       <c r="D3" s="1">
-        <v>473.3</v>
+        <f>473.3+28.8</f>
+        <v>502.1</v>
       </c>
       <c r="E3" s="1">
-        <v>2891.6000000000004</v>
-      </c>
-      <c r="F3" s="6">
-        <f t="shared" ref="F3:F39" si="1">B3-E3</f>
-        <v>2147</v>
-      </c>
-      <c r="G3" s="14">
-        <v>1822</v>
-      </c>
-      <c r="H3" s="1">
+        <f>3223.8+42.8+98</f>
+        <v>3364.6000000000004</v>
+      </c>
+      <c r="F3" s="1">
+        <f t="shared" ref="F3:F42" si="4">SUM(C3:E3)-B3</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="6">
+        <f t="shared" si="0"/>
+        <v>1674</v>
+      </c>
+      <c r="H3" s="11">
+        <v>1910</v>
+      </c>
+      <c r="I3" s="11">
+        <f t="shared" si="1"/>
+        <v>3599.6499470379536</v>
+      </c>
+      <c r="J3" s="1">
         <v>333</v>
       </c>
-      <c r="I3" s="4">
-        <v>532.9</v>
-      </c>
-      <c r="J3" s="1">
+      <c r="K3" s="4">
+        <f>404.8+99.3</f>
+        <v>504.1</v>
+      </c>
+      <c r="L3" s="1">
         <v>252.5</v>
       </c>
-      <c r="K3" s="1">
+      <c r="M3" s="1">
         <v>125.7</v>
       </c>
-      <c r="L3" s="1">
+      <c r="N3" s="1">
         <v>120.1</v>
       </c>
-      <c r="M3" s="1">
+      <c r="O3" s="1">
         <v>113.5</v>
       </c>
-      <c r="N3" s="1">
+      <c r="P3" s="1">
         <v>56</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
+      <c r="Q3" s="1">
+        <v>0</v>
+      </c>
+      <c r="R3" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="S3" s="1"/>
-      <c r="W3">
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="15"/>
+      <c r="Z3">
         <v>70.983096579396985</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>60075</v>
       </c>
       <c r="C4" s="1">
@@ -969,56 +1262,68 @@
       <c r="E4" s="1">
         <v>25252</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <f t="shared" si="0"/>
+        <v>34823</v>
+      </c>
+      <c r="H4" s="11">
+        <v>2100</v>
+      </c>
+      <c r="I4" s="11">
         <f t="shared" si="1"/>
-        <v>34823</v>
-      </c>
-      <c r="G4" s="14">
-        <v>2100</v>
-      </c>
-      <c r="H4" s="1">
+        <v>2407.296129454624</v>
+      </c>
+      <c r="J4" s="1">
         <v>450</v>
       </c>
-      <c r="I4" s="4">
+      <c r="K4" s="4">
         <v>1681</v>
       </c>
-      <c r="J4" s="1">
+      <c r="L4" s="1">
         <v>4258</v>
       </c>
-      <c r="K4" s="1">
+      <c r="M4" s="1">
         <v>478</v>
       </c>
-      <c r="L4" s="1">
+      <c r="N4" s="1">
         <v>934</v>
       </c>
-      <c r="M4" s="1">
+      <c r="O4" s="1">
         <v>2017</v>
       </c>
-      <c r="N4" s="1">
+      <c r="P4" s="1">
         <v>455</v>
       </c>
-      <c r="O4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="P4" s="1">
+      <c r="Q4" s="1">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S4" s="1">
         <v>2</v>
       </c>
-      <c r="Q4" s="1">
-        <f>P4*3*24</f>
+      <c r="T4" s="1">
+        <f>S4*3*24</f>
         <v>144</v>
       </c>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="W4">
+      <c r="U4" s="1"/>
+      <c r="V4" s="15"/>
+      <c r="Z4">
         <v>245.10201957552289</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>69298</v>
       </c>
       <c r="C5" s="1">
@@ -1030,60 +1335,73 @@
       <c r="E5" s="1">
         <v>36399</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="6">
+        <f t="shared" si="0"/>
+        <v>32899</v>
+      </c>
+      <c r="H5" s="11">
+        <v>2100</v>
+      </c>
+      <c r="I5" s="11">
         <f t="shared" si="1"/>
-        <v>32899</v>
-      </c>
-      <c r="G5" s="14">
-        <v>2100</v>
-      </c>
-      <c r="H5" s="1">
+        <v>2433.6282080275387</v>
+      </c>
+      <c r="J5" s="1">
         <v>333</v>
       </c>
-      <c r="I5" s="4">
+      <c r="K5" s="4">
         <v>1955</v>
       </c>
-      <c r="J5" s="1">
+      <c r="L5" s="1">
         <v>2943</v>
       </c>
-      <c r="K5" s="1">
+      <c r="M5" s="1">
         <v>478</v>
       </c>
-      <c r="L5" s="1">
+      <c r="N5" s="1">
         <v>1062</v>
       </c>
-      <c r="M5" s="1">
+      <c r="O5" s="1">
         <v>1006</v>
       </c>
-      <c r="N5" s="1">
+      <c r="P5" s="1">
         <v>455</v>
       </c>
-      <c r="O5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="P5" s="1">
+      <c r="Q5" s="1">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S5" s="1">
         <v>2</v>
       </c>
-      <c r="Q5" s="1">
-        <f>P5*3*24</f>
+      <c r="T5" s="1">
+        <f>S5*3*24</f>
         <v>144</v>
       </c>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="W5">
+      <c r="U5" s="1"/>
+      <c r="V5" s="15"/>
+      <c r="Z5">
         <v>263.24513290847375</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="1">
         <f>SUM(C6:E6)</f>
-        <v>89365</v>
+        <v>93037</v>
       </c>
       <c r="C6" s="1">
-        <v>9320</v>
+        <f>11198+1734+60</f>
+        <v>12992</v>
       </c>
       <c r="D6" s="1">
         <v>35894</v>
@@ -1091,51 +1409,63 @@
       <c r="E6" s="1">
         <v>44151</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="6">
+        <f t="shared" si="0"/>
+        <v>48886</v>
+      </c>
+      <c r="H6" s="11">
+        <v>3100</v>
+      </c>
+      <c r="I6" s="11">
         <f t="shared" si="1"/>
-        <v>45214</v>
-      </c>
-      <c r="G6" s="14">
-        <v>3100</v>
-      </c>
-      <c r="H6" s="1">
+        <v>2840.7581489184909</v>
+      </c>
+      <c r="J6" s="1">
         <v>450</v>
       </c>
-      <c r="I6" s="4">
+      <c r="K6" s="4">
         <v>1770</v>
       </c>
-      <c r="J6" s="1">
+      <c r="L6" s="1">
         <v>4969</v>
       </c>
-      <c r="K6" s="1">
+      <c r="M6" s="1">
         <v>385</v>
       </c>
-      <c r="L6" s="1">
+      <c r="N6" s="1">
         <v>307</v>
       </c>
-      <c r="M6" s="1">
+      <c r="O6" s="1">
         <v>420</v>
       </c>
-      <c r="N6" s="1">
-        <v>1469</v>
-      </c>
-      <c r="O6" s="1">
+      <c r="P6" s="1">
+        <f>1469+1734+60</f>
+        <v>3263</v>
+      </c>
+      <c r="Q6" s="1">
         <v>1878</v>
       </c>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
+      <c r="R6" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="S6" s="1"/>
-      <c r="W6">
-        <v>298.93979326948096</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="15"/>
+      <c r="Z6">
+        <v>305.01967149677409</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="1">
-        <f t="shared" si="0"/>
         <v>44821</v>
       </c>
       <c r="C7" s="1">
@@ -1147,1358 +1477,1686 @@
       <c r="E7" s="1">
         <v>22502</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
+        <f t="shared" si="0"/>
+        <v>22319</v>
+      </c>
+      <c r="H7" s="11">
+        <v>2260</v>
+      </c>
+      <c r="I7" s="11">
         <f t="shared" si="1"/>
-        <v>22319</v>
-      </c>
-      <c r="G7" s="14">
-        <v>2260</v>
-      </c>
-      <c r="H7" s="1">
+        <v>2592.325569657381</v>
+      </c>
+      <c r="J7" s="1">
         <v>379</v>
       </c>
-      <c r="I7" s="4">
+      <c r="K7" s="4">
         <v>2822</v>
       </c>
-      <c r="J7" s="1">
+      <c r="L7" s="1">
         <v>1749</v>
       </c>
-      <c r="K7" s="1">
+      <c r="M7" s="1">
         <v>204</v>
       </c>
-      <c r="L7" s="1">
-        <v>818</v>
-      </c>
-      <c r="M7" s="1">
+      <c r="N7" s="1">
+        <v>817</v>
+      </c>
+      <c r="O7" s="1">
+        <v>1</v>
+      </c>
+      <c r="P7" s="1">
         <v>265</v>
       </c>
-      <c r="N7" s="1">
-        <v>1</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="S7" s="1"/>
-      <c r="W7">
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="15"/>
+      <c r="Z7">
         <v>211.70970691019343</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="1">
-        <f t="shared" si="0"/>
-        <v>61503</v>
+        <v>60935</v>
       </c>
       <c r="C8" s="1">
-        <v>7542</v>
+        <f>9050+1764+694</f>
+        <v>11508</v>
       </c>
       <c r="D8" s="1">
-        <v>28475</v>
+        <f>28475-(65469-B8)</f>
+        <v>23941</v>
       </c>
       <c r="E8" s="1">
         <v>25486</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="6">
+        <f t="shared" si="0"/>
+        <v>35449</v>
+      </c>
+      <c r="H8" s="11">
+        <v>1900</v>
+      </c>
+      <c r="I8" s="11">
         <f t="shared" si="1"/>
-        <v>36017</v>
-      </c>
-      <c r="G8" s="14">
-        <v>1900</v>
-      </c>
-      <c r="H8" s="1">
+        <v>1923.7408979293918</v>
+      </c>
+      <c r="J8" s="1">
         <v>362</v>
       </c>
-      <c r="I8" s="4">
+      <c r="K8" s="4">
         <v>2015</v>
       </c>
-      <c r="J8" s="1">
+      <c r="L8" s="1">
         <v>2425</v>
       </c>
-      <c r="K8" s="1">
+      <c r="M8" s="1">
         <v>553</v>
       </c>
-      <c r="L8" s="1">
+      <c r="N8" s="1">
         <v>594</v>
       </c>
-      <c r="M8" s="1">
+      <c r="O8" s="1">
+        <f>777+295</f>
         <v>1072</v>
       </c>
-      <c r="N8" s="1">
-        <v>883</v>
-      </c>
-      <c r="O8" s="1">
+      <c r="P8" s="1">
+        <f>883+1764+694</f>
+        <v>3341</v>
+      </c>
+      <c r="Q8" s="1">
         <v>1508</v>
       </c>
-      <c r="P8" s="1">
+      <c r="R8" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S8" s="1">
         <v>2</v>
       </c>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="W8">
-        <v>247.99798386277257</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="15"/>
+      <c r="Z8">
+        <v>246.8501569778719</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="1">
-        <f t="shared" si="0"/>
-        <v>57620</v>
+        <v>56989</v>
       </c>
       <c r="C9" s="1">
-        <v>7412</v>
+        <f>8895+1741+698</f>
+        <v>11334</v>
       </c>
       <c r="D9" s="1">
-        <v>26375</v>
+        <f>26357-(61524-56989)</f>
+        <v>21822</v>
       </c>
       <c r="E9" s="1">
         <v>23833</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="6">
+        <f t="shared" si="0"/>
+        <v>33156</v>
+      </c>
+      <c r="H9" s="11">
+        <v>1900</v>
+      </c>
+      <c r="I9" s="11">
         <f t="shared" si="1"/>
-        <v>33787</v>
-      </c>
-      <c r="G9" s="14">
-        <v>1900</v>
-      </c>
-      <c r="H9" s="1">
+        <v>1865.0157347582269</v>
+      </c>
+      <c r="J9" s="1">
         <v>351</v>
       </c>
-      <c r="I9" s="4">
+      <c r="K9" s="4">
         <v>1985</v>
       </c>
-      <c r="J9" s="1">
+      <c r="L9" s="1">
         <v>2347</v>
       </c>
-      <c r="K9" s="1">
+      <c r="M9" s="1">
         <v>553</v>
       </c>
-      <c r="L9" s="1">
+      <c r="N9" s="1">
         <v>594</v>
       </c>
-      <c r="M9" s="1">
+      <c r="O9" s="1">
+        <f>777+289</f>
         <v>1066</v>
       </c>
-      <c r="N9" s="1">
-        <v>867</v>
-      </c>
-      <c r="O9" s="1">
+      <c r="P9" s="1">
+        <f>867+1741+698</f>
+        <v>3306</v>
+      </c>
+      <c r="Q9" s="1">
         <v>1483</v>
       </c>
-      <c r="P9" s="1">
+      <c r="R9" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="1">
         <v>2</v>
       </c>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="W9">
-        <v>240.04166305039632</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="15"/>
+      <c r="Z9">
+        <v>238.72368964977062</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="1">
-        <f t="shared" si="0"/>
-        <v>47150</v>
+        <v>45807</v>
       </c>
       <c r="C10" s="1">
-        <v>5970</v>
+        <f>7164+1286+717</f>
+        <v>9167</v>
       </c>
       <c r="D10" s="1">
-        <v>22028</v>
+        <f>22028-4540</f>
+        <v>17488</v>
       </c>
       <c r="E10" s="1">
         <v>19152</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="6">
+        <f t="shared" si="0"/>
+        <v>26655</v>
+      </c>
+      <c r="H10" s="11">
+        <v>1900</v>
+      </c>
+      <c r="I10" s="11">
         <f t="shared" si="1"/>
-        <v>27998</v>
-      </c>
-      <c r="G10" s="14">
-        <v>1900</v>
-      </c>
-      <c r="H10" s="1">
+        <v>1928.1559006099681</v>
+      </c>
+      <c r="J10" s="1">
         <v>363</v>
       </c>
-      <c r="I10" s="4">
+      <c r="K10" s="4">
         <v>1877</v>
       </c>
-      <c r="J10" s="1">
+      <c r="L10" s="1">
         <v>1125</v>
       </c>
-      <c r="K10" s="1">
+      <c r="M10" s="1">
         <v>553</v>
       </c>
-      <c r="L10" s="1">
+      <c r="N10" s="1">
         <v>594</v>
       </c>
-      <c r="M10" s="1">
+      <c r="O10" s="1">
+        <f>777+272</f>
         <v>1049</v>
       </c>
-      <c r="N10" s="1">
-        <v>772</v>
-      </c>
-      <c r="O10" s="1">
+      <c r="P10" s="1">
+        <f>772+1286+717</f>
+        <v>2775</v>
+      </c>
+      <c r="Q10" s="1">
         <v>1194</v>
       </c>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
+      <c r="R10" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="S10" s="1"/>
-      <c r="W10">
-        <v>217.14050750608465</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="15"/>
+      <c r="Z10">
+        <v>214.02569939145158</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A11" s="16" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="1">
-        <f t="shared" si="0"/>
-        <v>45180</v>
+        <v>43803</v>
       </c>
       <c r="C11" s="1">
-        <v>5912</v>
+        <f>7094+1264+719</f>
+        <v>9077</v>
       </c>
       <c r="D11" s="1">
-        <v>20956</v>
+        <f>20956-4542</f>
+        <v>16414</v>
       </c>
       <c r="E11" s="1">
         <v>18312</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="6">
+        <f t="shared" si="0"/>
+        <v>25491</v>
+      </c>
+      <c r="H11" s="11">
+        <v>1900</v>
+      </c>
+      <c r="I11" s="11">
         <f t="shared" si="1"/>
-        <v>26868</v>
-      </c>
-      <c r="G11" s="14">
-        <v>1900</v>
-      </c>
-      <c r="H11" s="1">
+        <v>1927.859237978244</v>
+      </c>
+      <c r="J11" s="1">
         <v>363</v>
       </c>
-      <c r="I11" s="4">
+      <c r="K11" s="4">
         <v>1860</v>
       </c>
-      <c r="J11" s="1">
+      <c r="L11" s="1">
         <v>1095</v>
       </c>
-      <c r="K11" s="1">
+      <c r="M11" s="1">
         <v>553</v>
       </c>
-      <c r="L11" s="1">
+      <c r="N11" s="1">
         <v>594</v>
       </c>
-      <c r="M11" s="1">
+      <c r="O11" s="1">
+        <f>777+269</f>
         <v>1046</v>
       </c>
-      <c r="N11" s="1">
-        <v>764</v>
-      </c>
-      <c r="O11" s="1">
+      <c r="P11" s="1">
+        <f>764+1264+719</f>
+        <v>2747</v>
+      </c>
+      <c r="Q11" s="1">
         <v>1182</v>
       </c>
-      <c r="P11" s="1">
+      <c r="R11" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="1">
         <v>4.5</v>
       </c>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="W11">
-        <v>212.55587500702021</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>23</v>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="15"/>
+      <c r="Z11">
+        <v>209.29166251907887</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="B12" s="1">
+        <v>11652</v>
+      </c>
+      <c r="C12" s="1">
+        <f>6975+229</f>
+        <v>7204</v>
+      </c>
+      <c r="D12" s="13">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>4447</v>
+      </c>
+      <c r="F12" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="6">
         <f t="shared" si="0"/>
-        <v>11180</v>
-      </c>
-      <c r="C12" s="1">
-        <v>6503</v>
-      </c>
-      <c r="D12" s="1">
-        <v>229</v>
-      </c>
-      <c r="E12" s="1">
-        <v>4448</v>
-      </c>
-      <c r="F12" s="6">
+        <v>7205</v>
+      </c>
+      <c r="H12" s="8">
+        <f t="shared" ref="H12:H39" si="5">J12*9.81*(LN(B12/(G12)))</f>
+        <v>2122.0616702809552</v>
+      </c>
+      <c r="I12" s="11">
         <f t="shared" si="1"/>
-        <v>6732</v>
-      </c>
-      <c r="G12" s="10">
-        <f>H12*9.81*(LN(B12/(F12)))</f>
-        <v>2239.2736279282085</v>
-      </c>
-      <c r="H12" s="1">
+        <v>2122.0616702809552</v>
+      </c>
+      <c r="J12" s="1">
         <v>450</v>
       </c>
-      <c r="I12" s="4">
-        <v>1186.3399999999999</v>
-      </c>
-      <c r="J12" s="1">
-        <v>918.21</v>
-      </c>
-      <c r="K12" s="1">
-        <v>663</v>
+      <c r="K12" s="4">
+        <v>1564</v>
       </c>
       <c r="L12" s="1">
-        <v>258.7</v>
+        <v>1186</v>
       </c>
       <c r="M12" s="1">
-        <v>459.04</v>
+        <v>343</v>
       </c>
       <c r="N12" s="1">
-        <v>1</v>
+        <v>1453</v>
       </c>
       <c r="O12" s="1">
+        <f>473+0</f>
+        <v>473</v>
+      </c>
+      <c r="P12" s="1">
+        <f>1053+431+229</f>
+        <v>1713</v>
+      </c>
+      <c r="Q12" s="1">
         <v>472</v>
       </c>
-      <c r="P12" s="1">
+      <c r="R12" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
         <v>5</v>
       </c>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="W12">
-        <v>105.73551910309043</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>25</v>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="15"/>
+      <c r="Z12">
+        <v>107.94443014810908</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="16" t="s">
+        <v>67</v>
       </c>
       <c r="B13" s="1">
-        <f>45000+7853</f>
-        <v>52853</v>
+        <v>53600</v>
       </c>
       <c r="C13" s="1">
-        <f>5848+1862+119</f>
-        <v>7829</v>
+        <f>8016+640+119</f>
+        <v>8775</v>
       </c>
       <c r="D13" s="1">
-        <f>7853+14221</f>
-        <v>22074</v>
+        <f>20862</f>
+        <v>20862</v>
       </c>
       <c r="E13" s="1">
-        <v>22950</v>
-      </c>
-      <c r="F13" s="6">
+        <v>23963</v>
+      </c>
+      <c r="F13" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="6">
+        <f t="shared" si="0"/>
+        <v>29637</v>
+      </c>
+      <c r="H13" s="8">
+        <f t="shared" si="5"/>
+        <v>2615.7037638902843</v>
+      </c>
+      <c r="I13" s="11">
         <f t="shared" si="1"/>
-        <v>29903</v>
-      </c>
-      <c r="G13" s="10">
-        <f>H13*9.81*(LN(B13/(F13)))</f>
-        <v>2514.3034845604184</v>
-      </c>
-      <c r="H13" s="1">
+        <v>2615.7037638902843</v>
+      </c>
+      <c r="J13" s="1">
         <v>450</v>
       </c>
-      <c r="I13" s="4">
-        <v>453</v>
-      </c>
-      <c r="J13" s="1">
-        <v>2969</v>
-      </c>
-      <c r="K13" s="1">
-        <v>288</v>
+      <c r="K13" s="4">
+        <v>535</v>
       </c>
       <c r="L13" s="1">
-        <v>519</v>
+        <v>3006</v>
       </c>
       <c r="M13" s="1">
-        <v>56</v>
+        <v>909</v>
       </c>
       <c r="N13" s="1">
-        <v>527</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>24</v>
+        <v>731</v>
+      </c>
+      <c r="O13" s="1">
+        <f>832+0</f>
+        <v>832</v>
       </c>
       <c r="P13" s="1">
+        <f>527+640+119+140</f>
+        <v>1426</v>
+      </c>
+      <c r="Q13" s="1">
+        <f>1336</f>
+        <v>1336</v>
+      </c>
+      <c r="R13" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S13" s="1">
         <v>3</v>
       </c>
-      <c r="Q13" s="1">
-        <f>P13*8.3</f>
+      <c r="T13" s="1">
+        <f>S13*8.3</f>
         <v>24.900000000000002</v>
       </c>
-      <c r="R13" s="1">
+      <c r="U13" s="1">
         <v>7.5</v>
       </c>
-      <c r="S13" s="1"/>
-      <c r="W13">
-        <v>229.8978033822855</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="9">
-        <f>5038-98-42.8</f>
-        <v>4897.2</v>
-      </c>
-      <c r="C14" s="9">
-        <v>1200.7</v>
-      </c>
-      <c r="D14" s="9">
-        <f>423.3+50</f>
-        <v>473.3</v>
-      </c>
-      <c r="E14" s="9">
-        <v>3223.8</v>
-      </c>
-      <c r="F14" s="6">
-        <f t="shared" si="1"/>
-        <v>1673.3999999999996</v>
-      </c>
-      <c r="G14" s="15">
-        <v>1910</v>
-      </c>
-      <c r="H14" s="9">
-        <v>353</v>
-      </c>
-      <c r="I14" s="11">
-        <v>404.8</v>
-      </c>
-      <c r="J14" s="9">
-        <v>252.5</v>
-      </c>
-      <c r="K14" s="9">
-        <v>125.7</v>
-      </c>
-      <c r="L14" s="9">
-        <v>120.1</v>
-      </c>
-      <c r="M14" s="16">
-        <v>113.5</v>
-      </c>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="W14">
-        <v>69.979997142040517</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="8">
+      <c r="V13" s="15"/>
+      <c r="Z13">
+        <v>231.5167380558045</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A14" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="7">
         <f>36272+18325</f>
         <v>54597</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C14" s="7">
         <v>6692</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D14" s="7">
         <v>18325</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E14" s="7">
         <v>29580</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F14" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="10">
+        <f t="shared" si="0"/>
+        <v>25017</v>
+      </c>
+      <c r="H14" s="19">
+        <f t="shared" si="5"/>
+        <v>2771.4549820453913</v>
+      </c>
+      <c r="I14" s="12">
         <f t="shared" si="1"/>
-        <v>25017</v>
-      </c>
-      <c r="G15" s="10">
-        <f>H15*9.81*(LN(B15/(F15)))</f>
         <v>2771.4549820453913</v>
       </c>
-      <c r="H15" s="7">
+      <c r="J14" s="7">
         <v>362</v>
       </c>
-      <c r="I15" s="4">
+      <c r="K14" s="9">
         <v>3757</v>
       </c>
-      <c r="J15" s="8">
+      <c r="L14" s="7">
         <v>1219</v>
       </c>
-      <c r="K15" s="8">
+      <c r="M14" s="7">
         <v>400</v>
       </c>
-      <c r="L15" s="8">
-        <v>200</v>
-      </c>
-      <c r="M15" s="7">
-        <v>0</v>
-      </c>
-      <c r="N15" s="8">
-        <v>166</v>
-      </c>
-      <c r="O15" s="8">
-        <v>0</v>
-      </c>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="8"/>
-      <c r="S15" s="1"/>
-      <c r="W15">
+      <c r="N14" s="7">
+        <v>199</v>
+      </c>
+      <c r="O14" s="7">
+        <v>1</v>
+      </c>
+      <c r="P14" s="7">
+        <f>431+685</f>
+        <v>1116</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>0</v>
+      </c>
+      <c r="R14" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="10"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="17"/>
+      <c r="V14" s="20"/>
+      <c r="W14" s="17"/>
+      <c r="X14" s="17"/>
+      <c r="Y14" s="17"/>
+      <c r="Z14" s="17">
         <v>233.66000941538968</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="1">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A15" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="1">
         <v>27021</v>
       </c>
-      <c r="C16" s="1">
-        <f>5663+563+782</f>
+      <c r="C15" s="1">
+        <f>5663+563</f>
+        <v>6226</v>
+      </c>
+      <c r="D15" s="21">
+        <v>782</v>
+      </c>
+      <c r="E15" s="1">
+        <v>20013</v>
+      </c>
+      <c r="F15" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="6">
+        <f t="shared" si="0"/>
         <v>7008</v>
       </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="1">
-        <v>20013</v>
-      </c>
-      <c r="F16" s="6">
+      <c r="H15" s="8">
+        <f t="shared" si="5"/>
+        <v>4792.5915224416285</v>
+      </c>
+      <c r="I15" s="11">
         <f t="shared" si="1"/>
-        <v>7008</v>
-      </c>
-      <c r="G16" s="10">
-        <f>H16*9.81*(LN(B16/(F16)))</f>
         <v>4792.5915224416285</v>
       </c>
-      <c r="H16" s="1">
+      <c r="J15" s="1">
         <v>362</v>
       </c>
-      <c r="I16" s="4">
+      <c r="K15" s="4">
         <v>2441</v>
       </c>
-      <c r="J16" s="1">
+      <c r="L15" s="1">
         <v>983</v>
       </c>
-      <c r="K16" s="1">
+      <c r="M15" s="1">
         <v>741</v>
       </c>
-      <c r="L16" s="1">
+      <c r="N15" s="1">
         <v>65</v>
       </c>
-      <c r="M16" s="1">
+      <c r="O15" s="1">
         <f>57+564</f>
         <v>621</v>
       </c>
-      <c r="N16" s="1">
-        <v>109</v>
-      </c>
-      <c r="O16" s="1">
+      <c r="P15" s="1">
+        <f>109+563</f>
+        <v>672</v>
+      </c>
+      <c r="Q15" s="1">
         <v>703</v>
       </c>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="W16">
+      <c r="R15" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="6"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z15">
         <v>164.38065579623412</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" s="1">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A16" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="1">
         <f>35054+10808</f>
         <v>45862</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C16" s="1">
         <f>6136+1033+486</f>
         <v>7655</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D16" s="1">
         <f>10808+2294</f>
         <v>13102</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E16" s="1">
         <v>25105</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F16" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="6">
+        <f t="shared" si="0"/>
+        <v>20757</v>
+      </c>
+      <c r="H16" s="8">
+        <f t="shared" si="5"/>
+        <v>3499.6096559997736</v>
+      </c>
+      <c r="I16" s="11">
         <f t="shared" si="1"/>
-        <v>20757</v>
-      </c>
-      <c r="G17" s="10">
-        <f>H17*9.81*(LN(B17/(F17)))</f>
         <v>3499.6096559997736</v>
       </c>
-      <c r="H17" s="1">
+      <c r="J16" s="1">
         <v>450</v>
       </c>
-      <c r="I17" s="4">
+      <c r="K16" s="4">
         <v>1113</v>
       </c>
-      <c r="J17" s="1">
-        <v>2632</v>
-      </c>
-      <c r="K17" s="1">
+      <c r="L16" s="1">
+        <v>2362</v>
+      </c>
+      <c r="M16" s="1">
         <v>468</v>
       </c>
-      <c r="L17" s="1">
+      <c r="N16" s="1">
         <v>69</v>
       </c>
-      <c r="M17" s="1">
+      <c r="O16" s="1">
         <f>281+88</f>
         <v>369</v>
       </c>
-      <c r="N17" s="1">
-        <v>842</v>
-      </c>
-      <c r="O17" s="1">
+      <c r="P16" s="1">
+        <f>640+92+486+1033</f>
+        <v>2251</v>
+      </c>
+      <c r="Q16" s="1">
         <v>1023</v>
       </c>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W17">
+      <c r="R16" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="6"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z16">
         <v>214.15415008820165</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="1">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A17" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="1">
         <f>10790+39791+31330</f>
         <v>81911</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C17" s="1">
         <f>9226+500+148</f>
         <v>9874</v>
       </c>
-      <c r="D18" s="1">
-        <f>31330+10790</f>
-        <v>42120</v>
-      </c>
-      <c r="E18" s="1">
-        <v>29756</v>
-      </c>
-      <c r="F18" s="6">
+      <c r="D17" s="1">
+        <f>31330+10790+148</f>
+        <v>42268</v>
+      </c>
+      <c r="E17" s="1">
+        <v>29769</v>
+      </c>
+      <c r="F17" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="6">
+        <f t="shared" si="0"/>
+        <v>52142</v>
+      </c>
+      <c r="H17" s="8">
+        <f t="shared" si="5"/>
+        <v>1993.8642207560945</v>
+      </c>
+      <c r="I17" s="11">
         <f t="shared" si="1"/>
-        <v>52155</v>
-      </c>
-      <c r="G18" s="10">
-        <f>H18*9.81*(LN(B18/(F18)))</f>
-        <v>1992.76373847382</v>
-      </c>
-      <c r="H18" s="1">
+        <v>1993.8642207560945</v>
+      </c>
+      <c r="J17" s="1">
         <v>450</v>
       </c>
-      <c r="I18" s="4">
+      <c r="K17" s="4">
         <v>2432</v>
       </c>
-      <c r="J18" s="1">
+      <c r="L17" s="1">
         <v>1826</v>
       </c>
-      <c r="K18" s="1">
+      <c r="M17" s="1">
         <v>336</v>
       </c>
-      <c r="L18" s="1">
+      <c r="N17" s="1">
         <v>145</v>
       </c>
-      <c r="M18" s="1">
+      <c r="O17" s="1">
         <f>1008+160</f>
         <v>1168</v>
       </c>
+      <c r="P17" s="1">
+        <f>1781+500+148</f>
+        <v>2429</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>1538</v>
+      </c>
+      <c r="R17" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="6"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="15"/>
+      <c r="Z17">
+        <v>286.20097833515524</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A18" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="1">
+        <v>37494</v>
+      </c>
+      <c r="C18" s="1">
+        <f>9050+1764+694</f>
+        <v>11508</v>
+      </c>
+      <c r="D18" s="21">
+        <v>500</v>
+      </c>
+      <c r="E18" s="1">
+        <v>25486</v>
+      </c>
+      <c r="F18" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="6">
+        <f t="shared" si="0"/>
+        <v>12008</v>
+      </c>
+      <c r="H18" s="8">
+        <f t="shared" si="5"/>
+        <v>4043.4468832931575</v>
+      </c>
+      <c r="I18" s="11">
+        <f t="shared" si="1"/>
+        <v>4043.4468832931575</v>
+      </c>
+      <c r="J18" s="1">
+        <v>362</v>
+      </c>
+      <c r="K18" s="4">
+        <v>2015</v>
+      </c>
+      <c r="L18" s="1">
+        <v>2425</v>
+      </c>
+      <c r="M18" s="1">
+        <v>553</v>
+      </c>
       <c r="N18" s="1">
-        <v>1781</v>
+        <v>594</v>
       </c>
       <c r="O18" s="1">
-        <v>1538</v>
-      </c>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-      <c r="W18">
-        <v>286.20097833515524</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="1">
-        <v>37494</v>
-      </c>
-      <c r="C19" s="1">
-        <v>9050</v>
-      </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="1">
-        <v>25486</v>
-      </c>
-      <c r="F19" s="6">
-        <f t="shared" si="1"/>
-        <v>12008</v>
-      </c>
-      <c r="G19" s="10">
-        <f>H19*9.81*(LN(B19/(F19)))</f>
-        <v>4043.4468832931575</v>
-      </c>
-      <c r="H19" s="1">
-        <v>362</v>
-      </c>
-      <c r="I19" s="4">
-        <v>2015</v>
-      </c>
-      <c r="J19" s="1">
-        <v>2425</v>
-      </c>
-      <c r="K19" s="1">
-        <v>553</v>
-      </c>
-      <c r="L19" s="1">
-        <v>594</v>
-      </c>
-      <c r="M19" s="1">
         <f>777+295</f>
         <v>1072</v>
       </c>
+      <c r="P18" s="1">
+        <f>883+1764+694</f>
+        <v>3341</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>1508</v>
+      </c>
+      <c r="R18" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="6"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z18">
+        <v>193.63367475725909</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A19" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="1">
+        <v>35667</v>
+      </c>
+      <c r="C19" s="1">
+        <f>8895+1741+698</f>
+        <v>11334</v>
+      </c>
+      <c r="D19" s="21">
+        <v>500</v>
+      </c>
+      <c r="E19" s="1">
+        <v>23833</v>
+      </c>
+      <c r="F19" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="6">
+        <f t="shared" si="0"/>
+        <v>11834</v>
+      </c>
+      <c r="H19" s="8">
+        <f t="shared" si="5"/>
+        <v>3798.8288213551818</v>
+      </c>
+      <c r="I19" s="11">
+        <f t="shared" si="1"/>
+        <v>3798.8288213551818</v>
+      </c>
+      <c r="J19" s="1">
+        <v>351</v>
+      </c>
+      <c r="K19" s="4">
+        <v>1985</v>
+      </c>
+      <c r="L19" s="1">
+        <v>2347</v>
+      </c>
+      <c r="M19" s="1">
+        <v>553</v>
+      </c>
       <c r="N19" s="1">
-        <v>883</v>
+        <v>594</v>
       </c>
       <c r="O19" s="1">
-        <v>1508</v>
-      </c>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="W19">
-        <v>193.63367475725909</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="1">
-        <v>35667</v>
-      </c>
-      <c r="C20" s="1">
-        <v>8895</v>
-      </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="1">
-        <v>23883</v>
-      </c>
-      <c r="F20" s="6">
-        <f t="shared" si="1"/>
-        <v>11784</v>
-      </c>
-      <c r="G20" s="10">
-        <f>H20*9.81*(LN(B20/(F20)))</f>
-        <v>3813.4080200345998</v>
-      </c>
-      <c r="H20" s="1">
-        <v>351</v>
-      </c>
-      <c r="I20" s="4">
-        <v>1985</v>
-      </c>
-      <c r="J20" s="1">
-        <v>2347</v>
-      </c>
-      <c r="K20" s="1">
-        <v>553</v>
-      </c>
-      <c r="L20" s="1">
-        <v>594</v>
-      </c>
-      <c r="M20" s="1">
         <f>777+289</f>
         <v>1066</v>
       </c>
+      <c r="P19" s="1">
+        <f>867+1741+698</f>
+        <v>3306</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>1483</v>
+      </c>
+      <c r="R19" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="6"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z19">
+        <v>188.8570888264457</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A20" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="1">
+        <v>28819</v>
+      </c>
+      <c r="C20" s="1">
+        <f>7164+1286+717</f>
+        <v>9167</v>
+      </c>
+      <c r="D20" s="21">
+        <v>500</v>
+      </c>
+      <c r="E20" s="1">
+        <v>19152</v>
+      </c>
+      <c r="F20" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="6">
+        <f t="shared" si="0"/>
+        <v>9667</v>
+      </c>
+      <c r="H20" s="8">
+        <f t="shared" si="5"/>
+        <v>3761.1855959947816</v>
+      </c>
+      <c r="I20" s="11">
+        <f t="shared" si="1"/>
+        <v>3761.1855959947816</v>
+      </c>
+      <c r="J20" s="1">
+        <v>351</v>
+      </c>
+      <c r="K20" s="4">
+        <v>1877</v>
+      </c>
+      <c r="L20" s="1">
+        <v>1125</v>
+      </c>
+      <c r="M20" s="1">
+        <v>553</v>
+      </c>
       <c r="N20" s="1">
-        <v>867</v>
+        <v>594</v>
       </c>
       <c r="O20" s="1">
-        <v>1483</v>
-      </c>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="W20">
-        <v>188.8570888264457</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="1">
-        <v>28819</v>
-      </c>
-      <c r="C21" s="1">
-        <f>7164+1286</f>
-        <v>8450</v>
-      </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="1">
-        <v>19152</v>
-      </c>
-      <c r="F21" s="6">
-        <f t="shared" si="1"/>
-        <v>9667</v>
-      </c>
-      <c r="G21" s="10">
-        <f>H21*9.81*(LN(B21/(F21)))</f>
-        <v>3889.7731377381924</v>
-      </c>
-      <c r="H21" s="1">
-        <v>363</v>
-      </c>
-      <c r="I21" s="4">
-        <v>1877</v>
-      </c>
-      <c r="J21" s="1">
-        <v>1125</v>
-      </c>
-      <c r="K21" s="1">
-        <v>553</v>
-      </c>
-      <c r="L21" s="1">
-        <v>594</v>
-      </c>
-      <c r="M21" s="1">
         <f>777+272</f>
         <v>1049</v>
       </c>
-      <c r="N21" s="1">
-        <v>772</v>
-      </c>
-      <c r="O21" s="1">
+      <c r="P20" s="1">
+        <f>772+1286+717</f>
+        <v>2775</v>
+      </c>
+      <c r="Q20" s="1">
         <v>1194</v>
       </c>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="W21">
+      <c r="R20" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z20">
         <v>169.7615975419647</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="1">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A21" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="1">
         <f>34504+7755</f>
         <v>42259</v>
       </c>
-      <c r="C22" s="1">
-        <f>4722+95</f>
-        <v>4817</v>
-      </c>
-      <c r="D22" s="1">
+      <c r="C21" s="1">
+        <f>4722+95+655</f>
+        <v>5472</v>
+      </c>
+      <c r="D21" s="1">
         <f>7755+1590</f>
         <v>9345</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E21" s="1">
         <v>27442</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F21" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="6">
+        <f t="shared" si="0"/>
+        <v>14817</v>
+      </c>
+      <c r="H21" s="8">
+        <f t="shared" si="5"/>
+        <v>3320.8578885135848</v>
+      </c>
+      <c r="I21" s="11">
         <f t="shared" si="1"/>
-        <v>14817</v>
-      </c>
-      <c r="G22" s="10">
-        <f>H22*9.81*(LN(B22/(F22)))</f>
         <v>3320.8578885135848</v>
       </c>
-      <c r="H22" s="1">
+      <c r="J21" s="1">
         <v>323</v>
       </c>
-      <c r="I22" s="4">
-        <v>1101</v>
-      </c>
-      <c r="J22" s="1">
+      <c r="K21" s="4">
+        <v>1011</v>
+      </c>
+      <c r="L21" s="1">
         <v>1616</v>
       </c>
-      <c r="K22" s="1">
+      <c r="M21" s="1">
         <v>306</v>
       </c>
-      <c r="L22" s="1">
+      <c r="N21" s="1">
         <v>69</v>
       </c>
-      <c r="M22" s="1">
-        <f>999+156</f>
-        <v>1155</v>
-      </c>
-      <c r="N22" s="1">
-        <f>842</f>
-        <v>842</v>
-      </c>
-      <c r="O22" s="1">
-        <f>1257</f>
-        <v>1257</v>
-      </c>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-      <c r="S22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W22">
+      <c r="O21" s="1">
+        <f>124+162</f>
+        <v>286</v>
+      </c>
+      <c r="P21" s="1">
+        <f>555+655+95+92</f>
+        <v>1397</v>
+      </c>
+      <c r="Q21" s="1">
+        <f>787</f>
+        <v>787</v>
+      </c>
+      <c r="R21" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z21">
         <v>205.56993943667931</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="1">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A22" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="1">
         <f>34018+7812</f>
         <v>41830</v>
       </c>
-      <c r="C23" s="1">
-        <f>5621+1968</f>
-        <v>7589</v>
-      </c>
-      <c r="D23" s="1">
+      <c r="C22" s="1">
+        <f>5621+1968+95</f>
+        <v>7684</v>
+      </c>
+      <c r="D22" s="1">
         <f>7812+1590</f>
         <v>9402</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E22" s="1">
         <v>24744</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F22" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="6">
+        <f t="shared" si="0"/>
+        <v>17086</v>
+      </c>
+      <c r="H22" s="8">
+        <f t="shared" si="5"/>
+        <v>3188.3837747817079</v>
+      </c>
+      <c r="I22" s="11">
         <f t="shared" si="1"/>
-        <v>17086</v>
-      </c>
-      <c r="G23" s="10">
-        <f>H23*9.81*(LN(B23/(F23)))</f>
         <v>3188.3837747817079</v>
       </c>
-      <c r="H23" s="6">
+      <c r="J22" s="6">
         <v>363</v>
       </c>
-      <c r="I23" s="4">
+      <c r="K22" s="4">
         <v>1355</v>
       </c>
-      <c r="J23" s="1">
+      <c r="L22" s="1">
         <v>2013</v>
       </c>
-      <c r="K23" s="1">
+      <c r="M22" s="1">
         <v>306</v>
       </c>
-      <c r="L23" s="1">
+      <c r="N22" s="1">
         <v>69</v>
       </c>
-      <c r="M23" s="1">
+      <c r="O22" s="1">
         <f>124+141</f>
         <v>265</v>
       </c>
-      <c r="N23" s="1">
-        <f>584</f>
-        <v>584</v>
-      </c>
-      <c r="O23" s="1">
+      <c r="P22" s="1">
+        <f>584+1968+95+92</f>
+        <v>2739</v>
+      </c>
+      <c r="Q22" s="1">
         <f>937</f>
         <v>937</v>
       </c>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
-      <c r="S23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="W23">
+      <c r="R22" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z22">
         <v>204.52383724153034</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="1">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A23" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="1">
         <f>15154+7737</f>
         <v>22891</v>
       </c>
-      <c r="C24" s="1">
-        <f>2761</f>
-        <v>2761</v>
-      </c>
-      <c r="D24" s="1">
+      <c r="C23" s="1">
+        <f>2761+250+95</f>
+        <v>3106</v>
+      </c>
+      <c r="D23" s="1">
         <f>7737+1590</f>
         <v>9327</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E23" s="1">
         <f>10458</f>
         <v>10458</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F23" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="6">
+        <f t="shared" si="0"/>
+        <v>12433</v>
+      </c>
+      <c r="H23" s="8">
+        <f t="shared" si="5"/>
+        <v>1934.0987736564762</v>
+      </c>
+      <c r="I23" s="11">
         <f t="shared" si="1"/>
-        <v>12433</v>
-      </c>
-      <c r="G24" s="10">
-        <f>H24*9.81*(LN(B24/(F24)))</f>
         <v>1934.0987736564762</v>
       </c>
-      <c r="H24" s="1">
+      <c r="J23" s="1">
         <v>323</v>
       </c>
-      <c r="I24" s="4">
+      <c r="K23" s="4">
         <v>451</v>
       </c>
-      <c r="J24" s="1">
+      <c r="L23" s="1">
         <v>677</v>
       </c>
-      <c r="K24" s="1">
+      <c r="M23" s="1">
         <v>306</v>
       </c>
-      <c r="L24" s="1">
+      <c r="N23" s="1">
         <v>69</v>
       </c>
-      <c r="M24" s="1">
+      <c r="O23" s="1">
         <f>124+86</f>
         <v>210</v>
       </c>
-      <c r="N24" s="1">
-        <v>496</v>
-      </c>
-      <c r="O24" s="1">
+      <c r="P23" s="1">
+        <f>496+250+95+92</f>
+        <v>933</v>
+      </c>
+      <c r="Q23" s="1">
         <v>460</v>
       </c>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="W24">
+      <c r="R23" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="15"/>
+      <c r="Z23">
         <v>151.29771974487917</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" s="1">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A24" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="1">
         <f>15472+7667</f>
         <v>23139</v>
       </c>
-      <c r="C25" s="1">
-        <v>3442</v>
-      </c>
-      <c r="D25" s="1">
+      <c r="C24" s="1">
+        <f>3442+995+95</f>
+        <v>4532</v>
+      </c>
+      <c r="D24" s="1">
         <f>7667+1590</f>
         <v>9257</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E24" s="1">
         <v>9350</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F24" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="6">
+        <f t="shared" si="0"/>
+        <v>13789</v>
+      </c>
+      <c r="H24" s="8">
+        <f t="shared" si="5"/>
+        <v>1843.3612424096523</v>
+      </c>
+      <c r="I24" s="11">
         <f t="shared" si="1"/>
-        <v>13789</v>
-      </c>
-      <c r="G25" s="10">
-        <f>H25*9.81*(LN(B25/(F25)))</f>
         <v>1843.3612424096523</v>
       </c>
-      <c r="H25" s="6">
+      <c r="J24" s="6">
         <v>363</v>
       </c>
-      <c r="I25" s="4">
+      <c r="K24" s="4">
         <v>717</v>
       </c>
-      <c r="J25" s="1">
+      <c r="L24" s="1">
         <v>955</v>
       </c>
-      <c r="K25" s="1">
+      <c r="M24" s="1">
         <v>306</v>
       </c>
-      <c r="L25" s="1">
+      <c r="N24" s="1">
         <v>69</v>
       </c>
-      <c r="M25" s="1">
+      <c r="O24" s="1">
         <f>124+95</f>
         <v>219</v>
       </c>
-      <c r="N25" s="1">
-        <v>510</v>
-      </c>
-      <c r="O25" s="1">
+      <c r="P24" s="1">
+        <f>510+995+95+92</f>
+        <v>1692</v>
+      </c>
+      <c r="Q24" s="1">
         <v>574</v>
       </c>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-      <c r="W25">
+      <c r="R24" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="15"/>
+      <c r="Z24">
         <v>152.11508800904662</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="1">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A25" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="1">
         <f>13564+9600</f>
         <v>23164</v>
       </c>
-      <c r="C26" s="1">
-        <f>2761+250</f>
-        <v>3011</v>
-      </c>
-      <c r="D26" s="1">
+      <c r="C25" s="1">
+        <f>2761+250+95</f>
+        <v>3106</v>
+      </c>
+      <c r="D25" s="1">
         <v>9600</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E25" s="1">
         <v>10458</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F25" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="6">
+        <f t="shared" si="0"/>
+        <v>12706</v>
+      </c>
+      <c r="H25" s="8">
+        <f t="shared" si="5"/>
+        <v>1902.8416147795385</v>
+      </c>
+      <c r="I25" s="11">
         <f t="shared" si="1"/>
-        <v>12706</v>
-      </c>
-      <c r="G26" s="10">
-        <f>H26*9.81*(LN(B26/(F26)))</f>
         <v>1902.8416147795385</v>
       </c>
-      <c r="H26" s="1">
+      <c r="J25" s="1">
         <v>323</v>
       </c>
-      <c r="I26" s="4">
+      <c r="K25" s="4">
         <v>451</v>
       </c>
-      <c r="J26" s="1">
+      <c r="L25" s="1">
         <v>677</v>
       </c>
-      <c r="K26" s="1">
+      <c r="M25" s="1">
         <v>306</v>
       </c>
-      <c r="L26" s="1">
+      <c r="N25" s="1">
         <v>69</v>
       </c>
-      <c r="M26" s="1">
+      <c r="O25" s="1">
         <f>124+86</f>
         <v>210</v>
       </c>
-      <c r="N26" s="1">
-        <v>496</v>
-      </c>
-      <c r="O26" s="1">
+      <c r="P25" s="1">
+        <f>496+250+95+92</f>
+        <v>933</v>
+      </c>
+      <c r="Q25" s="1">
         <v>460</v>
       </c>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
-      <c r="S26" s="1"/>
-      <c r="W26">
+      <c r="R25" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="15"/>
+      <c r="Z25">
         <v>152.19724044804491</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" s="1">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A26" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="1">
         <f>13882+9313</f>
         <v>23195</v>
       </c>
-      <c r="C27" s="1">
-        <v>3442</v>
-      </c>
-      <c r="D27" s="1">
+      <c r="C26" s="1">
+        <f>3442+995+95</f>
+        <v>4532</v>
+      </c>
+      <c r="D26" s="1">
         <v>9313</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E26" s="1">
         <v>9350</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F26" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="6">
+        <f t="shared" si="0"/>
+        <v>13845</v>
+      </c>
+      <c r="H26" s="8">
+        <f t="shared" si="5"/>
+        <v>1837.5362833866116</v>
+      </c>
+      <c r="I26" s="11">
         <f t="shared" si="1"/>
-        <v>13845</v>
-      </c>
-      <c r="G27" s="10">
-        <f>H27*9.81*(LN(B27/(F27)))</f>
         <v>1837.5362833866116</v>
       </c>
-      <c r="H27" s="6">
+      <c r="J26" s="6">
         <v>363</v>
       </c>
-      <c r="I27" s="4">
+      <c r="K26" s="4">
         <v>717</v>
       </c>
-      <c r="J27" s="1">
+      <c r="L26" s="1">
         <v>955</v>
       </c>
-      <c r="K27" s="1">
+      <c r="M26" s="1">
         <v>306</v>
       </c>
-      <c r="L27" s="1">
+      <c r="N26" s="1">
         <v>69</v>
       </c>
-      <c r="M27" s="1">
+      <c r="O26" s="1">
         <f>124+95</f>
         <v>219</v>
       </c>
+      <c r="P26" s="1">
+        <f>510+995+95+92</f>
+        <v>1692</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>574</v>
+      </c>
+      <c r="R26" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="15"/>
+      <c r="Z26">
+        <v>152.29904792873788</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A27" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="1">
+        <f>13564+9600</f>
+        <v>23164</v>
+      </c>
+      <c r="C27" s="1">
+        <f>2761+250+95</f>
+        <v>3106</v>
+      </c>
+      <c r="D27" s="1">
+        <f>9600</f>
+        <v>9600</v>
+      </c>
+      <c r="E27" s="1">
+        <v>10458</v>
+      </c>
+      <c r="F27" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="6">
+        <f t="shared" si="0"/>
+        <v>12706</v>
+      </c>
+      <c r="H27" s="8">
+        <f t="shared" si="5"/>
+        <v>1902.8416147795385</v>
+      </c>
+      <c r="I27" s="11">
+        <f t="shared" si="1"/>
+        <v>1902.8416147795385</v>
+      </c>
+      <c r="J27" s="1">
+        <v>323</v>
+      </c>
+      <c r="K27" s="4">
+        <v>451</v>
+      </c>
+      <c r="L27" s="1">
+        <v>677</v>
+      </c>
+      <c r="M27" s="1">
+        <v>306</v>
+      </c>
       <c r="N27" s="1">
-        <v>510</v>
+        <v>69</v>
       </c>
       <c r="O27" s="1">
-        <v>574</v>
-      </c>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
+        <f>124+86</f>
+        <v>210</v>
+      </c>
+      <c r="P27" s="1">
+        <f>496+250+95+92</f>
+        <v>933</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>460</v>
+      </c>
+      <c r="R27" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="S27" s="1"/>
-      <c r="W27">
-        <v>152.29904792873788</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>48</v>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="15"/>
+      <c r="Z27">
+        <v>152.19724044804491</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A28" s="16" t="s">
+        <v>46</v>
       </c>
       <c r="B28" s="1">
+        <f>33067+14451</f>
+        <v>47518</v>
+      </c>
+      <c r="C28" s="1">
+        <f>4739+658+95</f>
+        <v>5492</v>
+      </c>
+      <c r="D28" s="1">
+        <v>14451</v>
+      </c>
+      <c r="E28" s="1">
+        <v>27575</v>
+      </c>
+      <c r="F28" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="6">
+        <f t="shared" si="0"/>
+        <v>19943</v>
+      </c>
+      <c r="H28" s="8">
+        <f t="shared" si="5"/>
+        <v>3091.7944374111398</v>
+      </c>
+      <c r="I28" s="11">
+        <f t="shared" si="1"/>
+        <v>3091.7944374111398</v>
+      </c>
+      <c r="J28" s="6">
+        <v>363</v>
+      </c>
+      <c r="K28" s="4">
+        <v>1017</v>
+      </c>
+      <c r="L28" s="1">
+        <v>1624</v>
+      </c>
+      <c r="M28" s="1">
+        <v>306</v>
+      </c>
+      <c r="N28" s="1">
+        <v>69</v>
+      </c>
+      <c r="O28" s="1">
+        <f>124+162</f>
+        <v>286</v>
+      </c>
+      <c r="P28" s="1">
+        <f>555+658+95+92</f>
+        <v>1400</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>790</v>
+      </c>
+      <c r="R28" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="1"/>
+      <c r="V28" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z28">
+        <v>217.98623809772945</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A29" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="1">
         <f>33067+14234</f>
         <v>47301</v>
       </c>
-      <c r="C28" s="1">
-        <f>4739+658</f>
-        <v>5397</v>
-      </c>
-      <c r="D28" s="1">
+      <c r="C29" s="1">
+        <f>4739+658+95</f>
+        <v>5492</v>
+      </c>
+      <c r="D29" s="1">
+        <f>14234</f>
         <v>14234</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E29" s="1">
         <v>27575</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F29" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G29" s="6">
+        <f t="shared" si="0"/>
+        <v>19726</v>
+      </c>
+      <c r="H29" s="8">
+        <f t="shared" si="5"/>
+        <v>2771.2643882136222</v>
+      </c>
+      <c r="I29" s="11">
         <f t="shared" si="1"/>
-        <v>19726</v>
-      </c>
-      <c r="G28" s="10">
-        <f>H28*9.81*(LN(B28/(F28)))</f>
         <v>2771.2643882136222</v>
       </c>
-      <c r="H28" s="1">
+      <c r="J29" s="6">
         <v>323</v>
       </c>
-      <c r="I28" s="4">
+      <c r="K29" s="4">
         <v>1017</v>
       </c>
-      <c r="J28" s="1">
+      <c r="L29" s="1">
         <v>1624</v>
       </c>
-      <c r="K28" s="1">
+      <c r="M29" s="1">
         <v>306</v>
       </c>
-      <c r="L28" s="1">
+      <c r="N29" s="1">
         <v>69</v>
       </c>
-      <c r="M28" s="1">
+      <c r="O29" s="1">
         <f>124+162</f>
         <v>286</v>
       </c>
-      <c r="N28" s="1">
-        <v>555</v>
-      </c>
-      <c r="O28" s="1">
+      <c r="P29" s="1">
+        <f>555+658+95+92</f>
+        <v>1400</v>
+      </c>
+      <c r="Q29" s="1">
+        <f>790</f>
         <v>790</v>
       </c>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
-      <c r="S28" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="W28">
+      <c r="R29" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="1"/>
+      <c r="V29" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z29">
         <v>217.48793069961377</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B29" s="1">
-        <f>32700+14415</f>
-        <v>47115</v>
-      </c>
-      <c r="C29" s="1">
-        <f>5655+1981</f>
-        <v>7636</v>
-      </c>
-      <c r="D29" s="1">
-        <v>14415</v>
-      </c>
-      <c r="E29" s="1">
-        <v>24969</v>
-      </c>
-      <c r="F29" s="6">
-        <f t="shared" si="1"/>
-        <v>22146</v>
-      </c>
-      <c r="G29" s="10">
-        <f>H29*9.81*(LN(B29/(F29)))</f>
-        <v>2688.3445036070134</v>
-      </c>
-      <c r="H29" s="6">
-        <v>363</v>
-      </c>
-      <c r="I29" s="4">
-        <v>1364</v>
-      </c>
-      <c r="J29" s="1">
-        <v>2027</v>
-      </c>
-      <c r="K29" s="1">
-        <v>306</v>
-      </c>
-      <c r="L29" s="1">
-        <v>69</v>
-      </c>
-      <c r="M29" s="1">
-        <f>124+142</f>
-        <v>266</v>
-      </c>
-      <c r="N29" s="1">
-        <f>589</f>
-        <v>589</v>
-      </c>
-      <c r="O29" s="1">
-        <v>942</v>
-      </c>
-      <c r="P29" s="1"/>
-      <c r="S29" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="W29">
-        <v>217.05989956691678</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>51</v>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A30" s="16" t="s">
+        <v>48</v>
       </c>
       <c r="B30" s="1">
         <f>14030+5550</f>
         <v>19580</v>
       </c>
       <c r="C30" s="1">
-        <f>4690+990</f>
-        <v>5680</v>
+        <f>4690+990+950</f>
+        <v>6630</v>
       </c>
       <c r="D30" s="1">
         <f>5550+500</f>
@@ -2508,113 +3166,141 @@
         <f>6900</f>
         <v>6900</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="6">
+        <f t="shared" si="0"/>
+        <v>12680</v>
+      </c>
+      <c r="H30" s="8">
+        <f t="shared" si="5"/>
+        <v>1960.6465782897556</v>
+      </c>
+      <c r="I30" s="11">
         <f t="shared" si="1"/>
-        <v>12680</v>
-      </c>
-      <c r="G30" s="10">
-        <f>H30*9.81*(LN(B30/(F30)))</f>
         <v>1960.6465782897556</v>
       </c>
-      <c r="H30" s="1">
+      <c r="J30" s="1">
         <v>460</v>
       </c>
-      <c r="I30" s="4">
+      <c r="K30" s="4">
         <v>1150</v>
       </c>
-      <c r="J30" s="1">
+      <c r="L30" s="1">
         <v>750</v>
       </c>
-      <c r="K30" s="1">
+      <c r="M30" s="1">
         <v>630</v>
       </c>
-      <c r="L30" s="1">
+      <c r="N30" s="1">
         <v>80</v>
       </c>
-      <c r="M30" s="1">
+      <c r="O30" s="1">
         <f>740+60</f>
         <v>800</v>
       </c>
-      <c r="N30" s="1">
-        <f>440</f>
-        <v>440</v>
-      </c>
-      <c r="O30" s="1">
+      <c r="P30" s="1">
+        <f>440+990+950</f>
+        <v>2380</v>
+      </c>
+      <c r="Q30" s="1">
         <f>840</f>
         <v>840</v>
       </c>
-      <c r="P30" s="1"/>
-      <c r="W30">
+      <c r="R30" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="1"/>
+      <c r="V30" s="15"/>
+      <c r="Z30">
         <v>139.92855319769444</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>52</v>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A31" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="B31" s="1">
         <v>37848</v>
       </c>
       <c r="C31" s="1">
-        <f>9369+1885</f>
-        <v>11254</v>
-      </c>
-      <c r="D31" s="6"/>
+        <f>9369+1885+602</f>
+        <v>11856</v>
+      </c>
+      <c r="D31" s="21">
+        <v>500</v>
+      </c>
       <c r="E31" s="1">
         <v>25492</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="6">
+        <f t="shared" si="0"/>
+        <v>12356</v>
+      </c>
+      <c r="H31" s="8">
+        <f t="shared" si="5"/>
+        <v>3843.5847532961689</v>
+      </c>
+      <c r="I31" s="11">
         <f t="shared" si="1"/>
-        <v>12356</v>
-      </c>
-      <c r="G31" s="10">
-        <f t="shared" ref="G31:G39" si="2">H31*9.81*(LN(B31/(F31)))</f>
         <v>3843.5847532961689</v>
       </c>
-      <c r="H31" s="1">
+      <c r="J31" s="1">
         <v>350</v>
       </c>
-      <c r="I31" s="4">
+      <c r="K31" s="4">
         <v>2464</v>
       </c>
-      <c r="J31" s="1">
+      <c r="L31" s="1">
         <v>2422</v>
       </c>
-      <c r="K31" s="1">
+      <c r="M31" s="1">
         <v>553</v>
       </c>
-      <c r="L31" s="1">
+      <c r="N31" s="1">
         <v>594</v>
       </c>
-      <c r="M31" s="1">
+      <c r="O31" s="1">
         <f>777+106</f>
         <v>883</v>
       </c>
-      <c r="N31" s="1">
-        <f>892</f>
-        <v>892</v>
-      </c>
-      <c r="O31" s="1">
+      <c r="P31" s="1">
+        <f>892+1885+602</f>
+        <v>3379</v>
+      </c>
+      <c r="Q31" s="1">
         <v>1561</v>
       </c>
-      <c r="P31" s="1"/>
-      <c r="S31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="W31">
+      <c r="R31" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="1"/>
+      <c r="V31" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z31">
         <v>194.54562446891475</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>53</v>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A32" s="16" t="s">
+        <v>50</v>
       </c>
       <c r="B32" s="1">
         <f>39807+5193</f>
         <v>45000</v>
       </c>
       <c r="C32" s="1">
-        <v>8260</v>
+        <f>8260+1701+486</f>
+        <v>10447</v>
       </c>
       <c r="D32" s="1">
         <f>5193+4654</f>
@@ -2624,109 +3310,137 @@
         <f>24706</f>
         <v>24706</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G32" s="6">
+        <f t="shared" si="0"/>
+        <v>20294</v>
+      </c>
+      <c r="H32" s="8">
+        <f t="shared" si="5"/>
+        <v>3023.2703425059144</v>
+      </c>
+      <c r="I32" s="11">
         <f t="shared" si="1"/>
-        <v>20294</v>
-      </c>
-      <c r="G32" s="10">
-        <f t="shared" si="2"/>
         <v>3023.2703425059144</v>
       </c>
-      <c r="H32" s="17">
+      <c r="J32" s="13">
         <v>387</v>
       </c>
-      <c r="I32" s="4">
+      <c r="K32" s="4">
         <v>1932</v>
       </c>
-      <c r="J32" s="1">
+      <c r="L32" s="1">
         <v>2239</v>
       </c>
-      <c r="K32" s="1">
+      <c r="M32" s="1">
         <v>468</v>
       </c>
-      <c r="L32" s="1">
+      <c r="N32" s="1">
         <v>306</v>
       </c>
-      <c r="M32" s="1">
+      <c r="O32" s="1">
         <f>1119+88</f>
         <v>1207</v>
       </c>
-      <c r="N32" s="1">
-        <v>640</v>
-      </c>
-      <c r="O32" s="1">
+      <c r="P32" s="1">
+        <f>640+1701+486+91</f>
+        <v>2918</v>
+      </c>
+      <c r="Q32" s="1">
         <v>1377</v>
       </c>
-      <c r="P32" s="1"/>
-      <c r="W32">
+      <c r="R32" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="1"/>
+      <c r="V32" s="15"/>
+      <c r="Z32">
         <v>212.13203435596427</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>54</v>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A33" s="16" t="s">
+        <v>51</v>
       </c>
       <c r="B33" s="1">
         <f>40007+4994</f>
         <v>45001</v>
       </c>
       <c r="C33" s="1">
-        <f>8627+1502</f>
-        <v>10129</v>
+        <f>8627+1502+486</f>
+        <v>10615</v>
       </c>
       <c r="D33" s="1">
-        <f>4994+686</f>
-        <v>5680</v>
+        <f>4994+4686</f>
+        <v>9680</v>
       </c>
       <c r="E33" s="1">
         <v>24706</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="6">
+        <f t="shared" si="0"/>
+        <v>20295</v>
+      </c>
+      <c r="H33" s="8">
+        <f t="shared" si="5"/>
+        <v>3023.1676386581948</v>
+      </c>
+      <c r="I33" s="11">
         <f t="shared" si="1"/>
-        <v>20295</v>
-      </c>
-      <c r="G33" s="10">
-        <f t="shared" si="2"/>
         <v>3023.1676386581948</v>
       </c>
-      <c r="H33" s="17">
+      <c r="J33" s="13">
         <v>387</v>
       </c>
-      <c r="I33" s="4">
+      <c r="K33" s="4">
         <v>2203</v>
       </c>
-      <c r="J33" s="1">
+      <c r="L33" s="1">
         <v>2239</v>
       </c>
-      <c r="K33" s="1">
+      <c r="M33" s="1">
         <v>468</v>
       </c>
-      <c r="L33" s="1">
+      <c r="N33" s="1">
         <v>306</v>
       </c>
-      <c r="M33" s="1">
+      <c r="O33" s="1">
         <f>1104+88</f>
         <v>1192</v>
       </c>
-      <c r="N33" s="1">
-        <v>690</v>
-      </c>
-      <c r="O33" s="1">
+      <c r="P33" s="1">
+        <f>690+1502+486+91</f>
+        <v>2769</v>
+      </c>
+      <c r="Q33" s="1">
         <v>1438</v>
       </c>
-      <c r="P33" s="1"/>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>55</v>
+      <c r="R33" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="1"/>
+      <c r="V33" s="15"/>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A34" s="16" t="s">
+        <v>52</v>
       </c>
       <c r="B34" s="1">
         <f>39779+5220</f>
         <v>44999</v>
       </c>
       <c r="C34" s="1">
-        <f>8268+1583</f>
-        <v>9851</v>
+        <f>8268+1583+486</f>
+        <v>10337</v>
       </c>
       <c r="D34" s="1">
         <f>5220+4736</f>
@@ -2735,57 +3449,69 @@
       <c r="E34" s="1">
         <v>24706</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G34" s="6">
+        <f t="shared" si="0"/>
+        <v>20293</v>
+      </c>
+      <c r="H34" s="8">
+        <f t="shared" si="5"/>
+        <v>3023.3730536970029</v>
+      </c>
+      <c r="I34" s="11">
         <f t="shared" si="1"/>
-        <v>20293</v>
-      </c>
-      <c r="G34" s="10">
-        <f t="shared" si="2"/>
         <v>3023.3730536970029</v>
       </c>
-      <c r="H34" s="18">
+      <c r="J34" s="14">
         <v>387</v>
       </c>
-      <c r="I34" s="4">
+      <c r="K34" s="4">
         <v>2289</v>
       </c>
-      <c r="J34" s="1">
+      <c r="L34" s="1">
         <v>2239</v>
       </c>
-      <c r="K34" s="1">
+      <c r="M34" s="1">
         <v>468</v>
       </c>
-      <c r="L34" s="1">
+      <c r="N34" s="1">
         <v>354</v>
       </c>
-      <c r="M34" s="1">
+      <c r="O34" s="1">
         <f>1104+88</f>
         <v>1192</v>
       </c>
-      <c r="N34" s="1">
-        <f>257</f>
-        <v>257</v>
-      </c>
-      <c r="O34" s="1">
+      <c r="P34" s="1">
+        <f>257+1583+486+91</f>
+        <v>2417</v>
+      </c>
+      <c r="Q34" s="1">
         <f>1378</f>
         <v>1378</v>
       </c>
-      <c r="P34" s="1"/>
-      <c r="S34" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>57</v>
+      <c r="R34" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="1"/>
+      <c r="V34" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A35" s="16" t="s">
+        <v>54</v>
       </c>
       <c r="B35" s="1">
         <f>53643</f>
         <v>53643</v>
       </c>
       <c r="C35" s="1">
-        <f>6753+1033</f>
-        <v>7786</v>
+        <f>6753+1033+486</f>
+        <v>8272</v>
       </c>
       <c r="D35" s="1">
         <v>19000</v>
@@ -2793,44 +3519,58 @@
       <c r="E35" s="1">
         <v>26371</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F35" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="6">
+        <f t="shared" si="0"/>
+        <v>27272</v>
+      </c>
+      <c r="H35" s="8">
+        <f t="shared" si="5"/>
+        <v>2986.3670934036945</v>
+      </c>
+      <c r="I35" s="11">
         <f t="shared" si="1"/>
-        <v>27272</v>
-      </c>
-      <c r="G35" s="10">
-        <f t="shared" si="2"/>
         <v>2986.3670934036945</v>
       </c>
-      <c r="H35" s="1">
+      <c r="J35" s="1">
         <v>450</v>
       </c>
-      <c r="I35" s="4">
+      <c r="K35" s="4">
         <v>1113</v>
       </c>
-      <c r="J35" s="1">
+      <c r="L35" s="1">
         <v>2362</v>
       </c>
-      <c r="K35" s="1">
+      <c r="M35" s="1">
         <v>468</v>
       </c>
-      <c r="L35" s="1">
+      <c r="N35" s="1">
         <v>69</v>
       </c>
-      <c r="M35" s="1">
+      <c r="O35" s="1">
         <f>281+88</f>
         <v>369</v>
       </c>
-      <c r="N35" s="1">
-        <v>640</v>
-      </c>
-      <c r="O35" s="1">
+      <c r="P35" s="1">
+        <f>640+1033+486+92</f>
+        <v>2251</v>
+      </c>
+      <c r="Q35" s="1">
         <v>1640</v>
       </c>
-      <c r="P35" s="1"/>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>58</v>
+      <c r="R35" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="1"/>
+      <c r="V35" s="15"/>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A36" s="16" t="s">
+        <v>55</v>
       </c>
       <c r="B36" s="1">
         <f>45001+4971</f>
@@ -2848,45 +3588,58 @@
         <f>28043</f>
         <v>28043</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F36" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="6">
+        <f t="shared" si="0"/>
+        <v>21929</v>
+      </c>
+      <c r="H36" s="8">
+        <f t="shared" si="5"/>
+        <v>3636.0156688434217</v>
+      </c>
+      <c r="I36" s="11">
         <f t="shared" si="1"/>
-        <v>21929</v>
-      </c>
-      <c r="G36" s="10">
-        <f t="shared" si="2"/>
         <v>3636.0156688434217</v>
       </c>
-      <c r="H36" s="1">
+      <c r="J36" s="1">
         <v>450</v>
       </c>
-      <c r="I36" s="4">
+      <c r="K36" s="4">
         <v>4545</v>
       </c>
-      <c r="J36" s="1">
+      <c r="L36" s="1">
         <v>3111</v>
       </c>
-      <c r="K36" s="1">
+      <c r="M36" s="1">
         <v>934</v>
       </c>
-      <c r="L36" s="1">
+      <c r="N36" s="1">
         <v>441</v>
       </c>
-      <c r="M36" s="1">
+      <c r="O36" s="1">
         <f>156+180</f>
         <v>336</v>
       </c>
-      <c r="N36" s="1">
-        <f>946</f>
-        <v>946</v>
-      </c>
-      <c r="O36" s="1">
+      <c r="P36" s="1">
+        <f>429+3671</f>
+        <v>4100</v>
+      </c>
+      <c r="Q36" s="1">
         <v>1864</v>
       </c>
-      <c r="P36" s="1"/>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>59</v>
+      <c r="R36" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="1"/>
+      <c r="V36" s="15"/>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A37" s="16" t="s">
+        <v>56</v>
       </c>
       <c r="B37" s="1">
         <f>45001+4971</f>
@@ -2904,52 +3657,66 @@
         <f>28043</f>
         <v>28043</v>
       </c>
-      <c r="F37" s="6">
+      <c r="F37" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="6">
+        <f t="shared" si="0"/>
+        <v>21929</v>
+      </c>
+      <c r="H37" s="8">
+        <f t="shared" si="5"/>
+        <v>3636.0156688434217</v>
+      </c>
+      <c r="I37" s="11">
         <f t="shared" si="1"/>
-        <v>21929</v>
-      </c>
-      <c r="G37" s="10">
-        <f t="shared" si="2"/>
         <v>3636.0156688434217</v>
       </c>
-      <c r="H37" s="1">
+      <c r="J37" s="1">
         <v>450</v>
       </c>
-      <c r="I37" s="4">
+      <c r="K37" s="4">
         <v>4430</v>
       </c>
-      <c r="J37" s="1">
+      <c r="L37" s="1">
         <v>3182</v>
       </c>
-      <c r="K37" s="1">
+      <c r="M37" s="1">
         <v>934</v>
       </c>
-      <c r="L37" s="1">
+      <c r="N37" s="1">
         <v>441</v>
       </c>
-      <c r="M37" s="1">
+      <c r="O37" s="1">
         <f>156+180</f>
         <v>336</v>
       </c>
-      <c r="N37" s="1">
-        <v>429</v>
-      </c>
-      <c r="O37" s="1">
+      <c r="P37" s="1">
+        <f>429+3671</f>
+        <v>4100</v>
+      </c>
+      <c r="Q37" s="1">
         <v>1696</v>
       </c>
-      <c r="P37" s="1"/>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
-        <v>60</v>
+      <c r="R37" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="1"/>
+      <c r="V37" s="15"/>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A38" s="16" t="s">
+        <v>57</v>
       </c>
       <c r="B38" s="1">
         <f>45000+5005</f>
         <v>50005</v>
       </c>
       <c r="C38" s="1">
-        <f>16575+2445</f>
-        <v>19020</v>
+        <f>13575+2445</f>
+        <v>16020</v>
       </c>
       <c r="D38" s="1">
         <f>937+5005</f>
@@ -2959,46 +3726,59 @@
         <f>28043</f>
         <v>28043</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F38" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="6">
+        <f t="shared" si="0"/>
+        <v>21962</v>
+      </c>
+      <c r="H38" s="8">
+        <f t="shared" si="5"/>
+        <v>3632.2917133551828</v>
+      </c>
+      <c r="I38" s="11">
         <f t="shared" si="1"/>
-        <v>21962</v>
-      </c>
-      <c r="G38" s="10">
-        <f t="shared" si="2"/>
         <v>3632.2917133551828</v>
       </c>
-      <c r="H38" s="1">
+      <c r="J38" s="1">
         <v>450</v>
       </c>
-      <c r="I38" s="4">
+      <c r="K38" s="4">
         <f>6565</f>
         <v>6565</v>
       </c>
-      <c r="J38" s="1">
+      <c r="L38" s="1">
         <v>2889</v>
       </c>
-      <c r="K38" s="1">
+      <c r="M38" s="1">
         <v>934</v>
       </c>
-      <c r="L38" s="1">
+      <c r="N38" s="1">
         <v>441</v>
       </c>
-      <c r="M38" s="1">
+      <c r="O38" s="1">
         <f>156+180</f>
         <v>336</v>
       </c>
-      <c r="N38" s="1">
-        <f>446</f>
-        <v>446</v>
-      </c>
-      <c r="O38" s="1">
+      <c r="P38" s="1">
+        <f>446+2445</f>
+        <v>2891</v>
+      </c>
+      <c r="Q38" s="1">
         <v>1964</v>
       </c>
-      <c r="P38" s="1"/>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
-        <v>61</v>
+      <c r="R38" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S38" s="1"/>
+      <c r="V38" s="15"/>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A39" s="16" t="s">
+        <v>58</v>
       </c>
       <c r="B39" s="1">
         <f>45000+4971</f>
@@ -3016,44 +3796,58 @@
         <f>28043</f>
         <v>28043</v>
       </c>
-      <c r="F39" s="6">
+      <c r="F39" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="6">
+        <f t="shared" si="0"/>
+        <v>21928</v>
+      </c>
+      <c r="H39" s="8">
+        <f t="shared" si="5"/>
+        <v>3636.1286418487784</v>
+      </c>
+      <c r="I39" s="11">
         <f t="shared" si="1"/>
-        <v>21928</v>
-      </c>
-      <c r="G39" s="10">
-        <f t="shared" si="2"/>
         <v>3636.1286418487784</v>
       </c>
-      <c r="H39" s="1">
+      <c r="J39" s="1">
         <v>450</v>
       </c>
-      <c r="I39" s="4">
+      <c r="K39" s="4">
         <v>1856</v>
       </c>
-      <c r="J39" s="1">
+      <c r="L39" s="1">
         <v>2578</v>
       </c>
-      <c r="K39" s="1">
+      <c r="M39" s="1">
         <v>934</v>
       </c>
-      <c r="L39" s="1">
+      <c r="N39" s="1">
         <v>441</v>
       </c>
-      <c r="M39" s="1">
+      <c r="O39" s="1">
         <f>156+180</f>
         <v>336</v>
       </c>
-      <c r="N39" s="1">
-        <v>706</v>
-      </c>
-      <c r="O39" s="1">
+      <c r="P39" s="1">
+        <f>706+2889</f>
+        <v>3595</v>
+      </c>
+      <c r="Q39" s="1">
         <v>1280</v>
       </c>
-      <c r="P39" s="1"/>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
-        <v>62</v>
+      <c r="R39" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="1"/>
+      <c r="V39" s="15"/>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A40" s="16" t="s">
+        <v>59</v>
       </c>
       <c r="B40" s="1">
         <f>45001+4971</f>
@@ -3070,96 +3864,123 @@
       <c r="E40" s="1">
         <v>28043</v>
       </c>
-      <c r="F40" s="6">
-        <f t="shared" ref="F40:F43" si="3">B40-E40</f>
+      <c r="F40" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G40" s="6">
+        <f t="shared" si="0"/>
         <v>21929</v>
       </c>
-      <c r="G40" s="10">
-        <f t="shared" ref="G40:G43" si="4">H40*9.81*(LN(B40/(F40)))</f>
+      <c r="H40" s="8">
+        <f>J40*9.81*(LN(B40/(G40)))</f>
         <v>3636.0156688434217</v>
       </c>
-      <c r="H40" s="1">
+      <c r="I40" s="11">
+        <f t="shared" si="1"/>
+        <v>3636.0156688434217</v>
+      </c>
+      <c r="J40" s="1">
         <v>450</v>
       </c>
-      <c r="I40" s="4">
+      <c r="K40" s="4">
         <v>1638</v>
       </c>
-      <c r="J40" s="1">
+      <c r="L40" s="1">
         <v>2601</v>
       </c>
-      <c r="K40" s="1">
+      <c r="M40" s="1">
         <v>934</v>
       </c>
-      <c r="L40" s="1">
+      <c r="N40" s="1">
         <v>441</v>
       </c>
-      <c r="M40" s="1">
+      <c r="O40" s="1">
         <f>156+180</f>
         <v>336</v>
       </c>
-      <c r="N40" s="1">
-        <v>548</v>
-      </c>
-      <c r="O40" s="1">
+      <c r="P40" s="1">
+        <f>548+2731</f>
+        <v>3279</v>
+      </c>
+      <c r="Q40" s="1">
         <v>1197</v>
       </c>
-      <c r="P40" s="1"/>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
-        <v>63</v>
+      <c r="R40" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="1"/>
+      <c r="V40" s="15"/>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A41" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="B41" s="1">
-        <f>6912</f>
-        <v>6912</v>
+        <v>6913</v>
       </c>
       <c r="C41" s="1">
-        <f>3087</f>
-        <v>3087</v>
-      </c>
-      <c r="D41" s="6"/>
+        <v>3088</v>
+      </c>
+      <c r="D41" s="21">
+        <v>480</v>
+      </c>
       <c r="E41" s="1">
         <f>3345</f>
         <v>3345</v>
       </c>
-      <c r="F41" s="6">
-        <f t="shared" si="3"/>
-        <v>3567</v>
-      </c>
-      <c r="G41" s="10">
+      <c r="F41" s="1">
         <f t="shared" si="4"/>
-        <v>2096.1568748948289</v>
-      </c>
-      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41" s="6">
+        <f t="shared" si="0"/>
+        <v>3568</v>
+      </c>
+      <c r="H41" s="8">
+        <f>J41*9.81*(LN(B41/(G41)))</f>
+        <v>2095.7270727971309</v>
+      </c>
+      <c r="I41" s="11">
+        <f t="shared" si="1"/>
+        <v>2095.7270727971309</v>
+      </c>
+      <c r="J41" s="1">
         <v>323</v>
       </c>
-      <c r="I41" s="4">
+      <c r="K41" s="4">
         <v>1050</v>
       </c>
-      <c r="J41" s="1">
+      <c r="L41" s="1">
         <v>479</v>
       </c>
-      <c r="K41" s="1">
+      <c r="M41" s="1">
         <v>244</v>
       </c>
-      <c r="L41" s="1">
+      <c r="N41" s="1">
         <v>273</v>
       </c>
-      <c r="M41" s="1">
+      <c r="O41" s="1">
         <f>323+217</f>
         <v>540</v>
       </c>
-      <c r="N41" s="1">
-        <v>0</v>
-      </c>
-      <c r="O41" s="1">
+      <c r="P41" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="1">
         <v>501</v>
       </c>
-      <c r="P41" s="1"/>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
-        <v>64</v>
+      <c r="R41" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="1"/>
+      <c r="V41" s="15"/>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A42" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="B42" s="1">
         <f>37668+6685</f>
@@ -3176,46 +3997,58 @@
         <v>26182</v>
       </c>
       <c r="F42" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G42" s="1">
+        <f t="shared" si="0"/>
         <v>18171</v>
       </c>
-      <c r="G42" s="14">
-        <f t="shared" si="4"/>
+      <c r="H42" s="11">
+        <f>J42*9.81*(LN(B42/(G42)))</f>
         <v>3939.2942323794919</v>
       </c>
-      <c r="H42" s="1">
+      <c r="I42" s="11">
+        <f t="shared" si="1"/>
+        <v>3939.2942323794919</v>
+      </c>
+      <c r="J42" s="1">
         <v>450</v>
       </c>
-      <c r="I42" s="4">
+      <c r="K42" s="4">
         <v>4939</v>
       </c>
-      <c r="J42" s="1">
+      <c r="L42" s="1">
         <v>2352</v>
       </c>
-      <c r="K42" s="1">
+      <c r="M42" s="1">
         <v>1563</v>
       </c>
-      <c r="L42" s="1">
+      <c r="N42" s="1">
         <v>263</v>
       </c>
-      <c r="M42" s="1">
+      <c r="O42" s="1">
         <f>700+340</f>
         <v>1040</v>
       </c>
-      <c r="N42" s="1">
+      <c r="P42" s="1">
         <v>1329</v>
       </c>
-      <c r="O42" s="1">
-        <v>0</v>
-      </c>
-      <c r="P42" s="1"/>
-      <c r="S42" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="Q42" s="1">
+        <v>0</v>
+      </c>
+      <c r="R42" s="1">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S42" s="1"/>
+      <c r="V42" s="15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B43" s="1">
         <v>11652</v>
@@ -3229,11 +4062,11 @@
         <v>4448</v>
       </c>
       <c r="F43" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="F40:F43" si="6">B43-E43</f>
         <v>7204</v>
       </c>
-      <c r="G43" s="14">
-        <f t="shared" si="4"/>
+      <c r="G43" s="11">
+        <f t="shared" ref="G40:G43" si="7">H43*9.81*(LN(B43/(F43)))</f>
         <v>2122.6744123181657</v>
       </c>
       <c r="H43" s="1">
@@ -3263,14 +4096,14 @@
       </c>
       <c r="P43" s="1"/>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
-      <c r="G44" s="14"/>
+      <c r="G44" s="11"/>
       <c r="H44" s="1"/>
       <c r="I44" s="4"/>
       <c r="J44" s="1"/>
@@ -3281,14 +4114,14 @@
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="14"/>
+      <c r="G45" s="11"/>
       <c r="H45" s="1"/>
       <c r="I45" s="4"/>
       <c r="J45" s="1"/>
@@ -3299,7 +4132,7 @@
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -3317,7 +4150,7 @@
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -3336,6 +4169,19 @@
       <c r="P47" s="1"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="R2:R42">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>